--- a/Калькулятор_ставки_часа.xlsx
+++ b/Калькулятор_ставки_часа.xlsx
@@ -984,7 +984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1657,6 +1657,12 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2432,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2459,7 +2465,7 @@
     <row r="4">
       <c r="A4" s="146" t="inlineStr">
         <is>
-          <t>ИЗ ЧЕГО СОСТОИТ ПРОДУКТ — три файла</t>
+          <t>ИЗ ЧЕГО СОСТОИТ ПРОДУКТ — четыре файла</t>
         </is>
       </c>
       <c r="B4" s="147" t="n"/>
@@ -2489,383 +2495,392 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="149" t="inlineStr">
-        <is>
-          <t>web/calc.html</t>
-        </is>
-      </c>
-      <c r="B7" s="152" t="inlineStr">
-        <is>
-          <t>ФОРМА. 23 вопроса, считает результат, показывает краткий итог и блок оплаты. Ставится на Tilda как HTML-блок. Иконки вшиты внутрь, внешних файлов не требует.</t>
+      <c r="A7" s="312" t="inlineStr">
+        <is>
+          <t>web/index.html</t>
+        </is>
+      </c>
+      <c r="B7" s="313" t="inlineStr">
+        <is>
+          <t>СТРАНИЦА ВХОДА. Первое, что видит человек: один экран — заголовок, три пользы, кнопка. Принимает реферальную метку и передаёт её в форму. Кто уже начинал, попадает сразу в форму.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="149" t="inlineStr">
         <is>
+          <t>web/calc.html</t>
+        </is>
+      </c>
+      <c r="B8" s="152" t="inlineStr">
+        <is>
+          <t>ФОРМА. Вопросы анкеты, кнопка расчёта и анимация расчёта. Больше ничего: краткий итог и блок оплаты вынесены. После расчёта открывается отчёт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="149" t="inlineStr">
+        <is>
           <t>web/report.html</t>
         </is>
       </c>
-      <c r="B8" s="152" t="inlineStr">
+      <c r="B9" s="152" t="inlineStr">
         <is>
           <t>ПОЛНЫЙ ОТЧЁТ. 10 блоков, открывается после оплаты. Данные принимает из формы. Тоже автономный файл.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-    </row>
     <row r="10">
-      <c r="A10" s="146" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="146" t="inlineStr">
         <is>
           <t>КАК УСТРОЕНА КНИГА — 27 листов</t>
         </is>
       </c>
-      <c r="B10" s="147" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="148" t="inlineStr">
+      <c r="B11" s="147" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="148" t="inlineStr">
         <is>
           <t>Лист</t>
         </is>
       </c>
-      <c r="B11" s="148" t="inlineStr">
+      <c r="B12" s="148" t="inlineStr">
         <is>
           <t>Назначение</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="149" t="inlineStr">
-        <is>
-          <t>00_Читать</t>
-        </is>
-      </c>
-      <c r="B12" s="152" t="inlineStr">
-        <is>
-          <t>Этот лист — карта проекта</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="149" t="inlineStr">
         <is>
-          <t>01_Глоссарий</t>
+          <t>00_Читать</t>
         </is>
       </c>
       <c r="B13" s="152" t="inlineStr">
         <is>
-          <t>Термины: что такое ставка, амортизация, юнит-экономика</t>
+          <t>Этот лист — карта проекта</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="149" t="inlineStr">
         <is>
-          <t>02_Параметры</t>
+          <t>01_Глоссарий</t>
         </is>
       </c>
       <c r="B14" s="152" t="inlineStr">
         <is>
-          <t>143 строки. Все входные величины и формулы через ID. ГЛАВНЫЙ лист для правки цифр</t>
+          <t>Термины: что такое ставка, амортизация, юнит-экономика</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="149" t="inlineStr">
         <is>
-          <t>03_Каталоги</t>
+          <t>02_Параметры</t>
         </is>
       </c>
       <c r="B15" s="152" t="inlineStr">
         <is>
-          <t>Оборудование, ПО, реклама — построчно, с ценами и сроками службы</t>
+          <t>143 строки. Все входные величины и формулы через ID. ГЛАВНЫЙ лист для правки цифр</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="149" t="inlineStr">
         <is>
-          <t>04_Итог / 05_Расчёт</t>
+          <t>03_Каталоги</t>
         </is>
       </c>
       <c r="B16" s="152" t="inlineStr">
         <is>
-          <t>Свод и расчёт по семи налоговым режимам</t>
+          <t>Оборудование, ПО, реклама — построчно, с ценами и сроками службы</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="149" t="inlineStr">
         <is>
-          <t>06_Отчёт</t>
+          <t>04_Итог / 05_Расчёт</t>
         </is>
       </c>
       <c r="B17" s="152" t="inlineStr">
         <is>
-          <t>Все цифры отчёта: доход по ролям, расходы, сценарии</t>
+          <t>Свод и расчёт по семи налоговым режимам</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="149" t="inlineStr">
         <is>
-          <t>07_Интерфейс / 08_UI / 08b / 08c</t>
+          <t>06_Отчёт</t>
         </is>
       </c>
       <c r="B18" s="152" t="inlineStr">
         <is>
-          <t>Структура формы и отчёта: какой блок за каким идёт</t>
+          <t>Все цифры отчёта: доход по ролям, расходы, сценарии</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="149" t="inlineStr">
         <is>
-          <t>09_Тексты</t>
+          <t>07_Интерфейс / 08_UI / 08b / 08c</t>
         </is>
       </c>
       <c r="B19" s="152" t="inlineStr">
         <is>
-          <t>514 надписей. Колонка «Где находится» — поверхность (форма, отчёт, подсказки). Есть автофильтр</t>
+          <t>Структура формы и отчёта: какой блок за каким идёт</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="149" t="inlineStr">
         <is>
-          <t>09b_Методика_цифр</t>
+          <t>09_Тексты</t>
         </is>
       </c>
       <c r="B20" s="152" t="inlineStr">
         <is>
-          <t>Как посчитана каждая цифра блока 09, откуда берутся рабочие паузы, правило округления</t>
+          <t>514 надписей. Колонка «Где находится» — поверхность (форма, отчёт, подсказки). Есть автофильтр</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="149" t="inlineStr">
         <is>
-          <t>09e_Как_считается</t>
+          <t>09b_Методика_цифр</t>
         </is>
       </c>
       <c r="B21" s="152" t="inlineStr">
         <is>
-          <t>Полная цепочка расчёта ставки часа: 10 шагов от календаря до цены, с формулами и проверкой сходимости</t>
+          <t>Как посчитана каждая цифра блока 09, откуда берутся рабочие паузы, правило округления</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="149" t="inlineStr">
         <is>
-          <t>09c_Палитра</t>
+          <t>09e_Как_считается</t>
         </is>
       </c>
       <c r="B22" s="152" t="inlineStr">
         <is>
-          <t>68 цветов. Единая система для формы и отчёта</t>
+          <t>Полная цепочка расчёта ставки часа: 10 шагов от календаря до цены, с формулами и проверкой сходимости</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="149" t="inlineStr">
         <is>
-          <t>10_Монетизация / 11_Ссылки</t>
+          <t>09c_Палитра</t>
         </is>
       </c>
       <c r="B23" s="152" t="inlineStr">
         <is>
-          <t>Цена продукта, источники данных</t>
+          <t>68 цветов. Единая система для формы и отчёта</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="149" t="inlineStr">
         <is>
+          <t>10_Монетизация / 11_Ссылки</t>
+        </is>
+      </c>
+      <c r="B24" s="152" t="inlineStr">
+        <is>
+          <t>Цена продукта, источники данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="149" t="inlineStr">
+        <is>
           <t>12_Диаграммы / 13_Сетка_скидок / 13b_Программа_лояльности / 14_Опрос</t>
         </is>
       </c>
-      <c r="B24" s="152" t="inlineStr">
+      <c r="B25" s="152" t="inlineStr">
         <is>
           <t>Данные для графиков, скидки за объём, ФОНД И ВСЯ ПРОГРАММА ЛОЯЛЬНОСТИ, опрос в форме</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="146" t="inlineStr">
+      <c r="A26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="146" t="inlineStr">
         <is>
           <t>ЧТО ГДЕ ПРАВИТЬ</t>
         </is>
       </c>
-      <c r="B26" s="147" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="148" t="inlineStr">
+      <c r="B27" s="147" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="148" t="inlineStr">
         <is>
           <t>Задача</t>
         </is>
       </c>
-      <c r="B27" s="148" t="inlineStr">
+      <c r="B28" s="148" t="inlineStr">
         <is>
           <t>Куда идти</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="149" t="inlineStr">
-        <is>
-          <t>Поменять текст надписи</t>
-        </is>
-      </c>
-      <c r="B28" s="152" t="inlineStr">
-        <is>
-          <t>09_Тексты → найти по ключу → колонка «Текст». Ключ виден в HTML как data-t="..."</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="149" t="inlineStr">
         <is>
-          <t>Поменять цифру или формулу</t>
+          <t>Поменять текст надписи</t>
         </is>
       </c>
       <c r="B29" s="152" t="inlineStr">
         <is>
-          <t>02_Параметры → колонка «Значение»</t>
+          <t>09_Тексты → найти по ключу → колонка «Текст». Ключ виден в HTML как data-t="..."</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="149" t="inlineStr">
         <is>
-          <t>Поменять цвет</t>
+          <t>Поменять цифру или формулу</t>
         </is>
       </c>
       <c r="B30" s="152" t="inlineStr">
         <is>
-          <t>09c_Палитра → HEX. Затем тот же токен в :root обоих HTML</t>
+          <t>02_Параметры → колонка «Значение»</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="149" t="inlineStr">
         <is>
-          <t>Добавить оборудование</t>
+          <t>Поменять цвет</t>
         </is>
       </c>
       <c r="B31" s="152" t="inlineStr">
         <is>
-          <t>03_Каталоги → новая строка с кодом формы</t>
+          <t>09c_Палитра → HEX. Затем тот же токен в :root обоих HTML</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="149" t="inlineStr">
         <is>
+          <t>Добавить оборудование</t>
+        </is>
+      </c>
+      <c r="B32" s="152" t="inlineStr">
+        <is>
+          <t>03_Каталоги → новая строка с кодом формы</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="149" t="inlineStr">
+        <is>
           <t>Изменить скидки, фонд, сертификаты</t>
         </is>
       </c>
-      <c r="B32" s="152" t="inlineStr">
+      <c r="B33" s="152" t="inlineStr">
         <is>
           <t>13b_Программа_лояльности → жёлтые ячейки. Остальное пересчитается формулами</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Изменить порядок блоков</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>08c_Структура_отчёта</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="146" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="146" t="inlineStr">
         <is>
           <t>ПЕРЕД ПУБЛИКАЦИЕЙ — обязательно</t>
         </is>
       </c>
-      <c r="B34" s="147" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="148" t="inlineStr">
+      <c r="B35" s="147" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="148" t="inlineStr">
         <is>
           <t>Что</t>
         </is>
       </c>
-      <c r="B35" s="148" t="inlineStr">
+      <c r="B36" s="148" t="inlineStr">
         <is>
           <t>Где в calc.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="149" t="inlineStr">
-        <is>
-          <t>DEV_NO_BLUR = false</t>
-        </is>
-      </c>
-      <c r="B36" s="152" t="inlineStr">
-        <is>
-          <t>сейчас true — отчёт не размыт, виден бесплатно</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="149" t="inlineStr">
         <is>
-          <t>YM_ID = номер счётчика</t>
+          <t>DEV_NO_BLUR = false</t>
         </is>
       </c>
       <c r="B37" s="152" t="inlineStr">
         <is>
-          <t>сейчас 0 — Яндекс.Метрика не подключена</t>
+          <t>сейчас true — отчёт не размыт, виден бесплатно</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="149" t="inlineStr">
         <is>
-          <t>PAY_URL = ссылка оплаты</t>
+          <t>YM_ID = номер счётчика</t>
         </is>
       </c>
       <c r="B38" s="152" t="inlineStr">
         <is>
-          <t>сейчас '#order' — заглушка</t>
+          <t>сейчас 0 — Яндекс.Метрика не подключена</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="149" t="inlineStr">
         <is>
+          <t>PAY_URL = ссылка оплаты</t>
+        </is>
+      </c>
+      <c r="B39" s="152" t="inlineStr">
+        <is>
+          <t>сейчас '#order' — заглушка</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="149" t="inlineStr">
+        <is>
           <t>Связка форма → отчёт</t>
         </is>
       </c>
-      <c r="B39" s="152" t="inlineStr">
+      <c r="B40" s="152" t="inlineStr">
         <is>
           <t>форма пока не передаёт данные в отчёт, отчёт показывает демо-набор</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-    </row>
     <row r="41">
-      <c r="A41" s="145" t="inlineStr">
+      <c r="A41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="145" t="inlineStr">
         <is>
           <t>Папка _архив — старые версии и черновики. Для работы не нужны, удалять не обязательно.</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2899,6 +2914,9 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4839,7 +4857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H646"/>
+  <dimension ref="A1:H649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4901,6 +4919,11 @@
           <t>Сколько на самом деле стоит ваш час</t>
         </is>
       </c>
+      <c r="H6" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: шапка анкеты приведена к отчёту, ключ заменён на rh_01 / rh_02 / rh_03 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4925,6 +4948,11 @@
           <t>Калькулятор для фотографов и видеографов. Считает ставку, которая покроет не только съёмку, но и обработку, продвижение, технику и налоги.</t>
         </is>
       </c>
+      <c r="H8" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: шапка анкеты приведена к отчёту, ключ заменён на rh_01 / rh_02 / rh_03 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -5042,7 +5070,7 @@
       </c>
       <c r="C18" s="113" t="inlineStr">
         <is>
-          <t>Режим и текущая ставка</t>
+          <t>Налоговый режим</t>
         </is>
       </c>
     </row>
@@ -5151,6 +5179,11 @@
           <t>Сколько вы берёте за час съёмки сейчас?</t>
         </is>
       </c>
+      <c r="H26" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: вопрос убран, остались заголовок и подзаголовок блока 03 — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5175,6 +5208,11 @@
           <t>Нужно, чтобы показать разницу между вашей текущей и расчётной ставкой. Можно оставить пустым.</t>
         </is>
       </c>
+      <c r="H28" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: вопрос убран, остались заголовок и подзаголовок блока 03 — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5388,7 +5426,12 @@
       </c>
       <c r="C46" s="113" t="inlineStr">
         <is>
-          <t>Длительность съёмки</t>
+          <t>Посчитаем ваше время</t>
+        </is>
+      </c>
+      <c r="H46" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -5415,6 +5458,11 @@
           <t>Ваш минимальный выезд. От него считается базовая ставка часа, а всё, что длиннее, — скидка за объём</t>
         </is>
       </c>
+      <c r="H48" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -5439,6 +5487,11 @@
           <t>Какая у вас минимальная продолжительность съёмки?</t>
         </is>
       </c>
+      <c r="H50" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -5535,6 +5588,11 @@
           <t>Как устроена ваша работа</t>
         </is>
       </c>
+      <c r="H58" s="297" t="inlineStr">
+        <is>
+          <t>ОБЪЕДИНЕНО: блок 05 слит с блоком 04, заголовок взят у него 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -5559,6 +5617,11 @@
           <t>Сколько часов вы тратите на обработку одного часа отснятого материала?</t>
         </is>
       </c>
+      <c r="H60" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -5631,6 +5694,11 @@
           <t>Сколько времени уходит на общение с клиентом по одному заказу?</t>
         </is>
       </c>
+      <c r="H66" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -5701,6 +5769,11 @@
       <c r="C72" s="113" t="inlineStr">
         <is>
           <t>Сколько часов в день вы тратите на продвижение?</t>
+        </is>
+      </c>
+      <c r="H72" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -7965,6 +8038,11 @@
           <t>Ваша расчётная ставка</t>
         </is>
       </c>
+      <c r="H252" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -7989,6 +8067,11 @@
           <t>за одну съёмку</t>
         </is>
       </c>
+      <c r="H254" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="27" t="inlineStr">
@@ -8006,6 +8089,11 @@
           <t>выручка в месяц</t>
         </is>
       </c>
+      <c r="H255" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="27" t="inlineStr">
@@ -8023,6 +8111,11 @@
           <t>съёмок в месяц</t>
         </is>
       </c>
+      <c r="H256" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -8047,6 +8140,11 @@
           <t>Куда уходит каждый час съёмки</t>
         </is>
       </c>
+      <c r="H258" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -8071,6 +8169,11 @@
           <t>Вам платят за час на площадке, но эти деньги покрывают всю работу вокруг него</t>
         </is>
       </c>
+      <c r="H260" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -8095,6 +8198,11 @@
           <t>Спасибо за поддержку!</t>
         </is>
       </c>
+      <c r="H262" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="27" t="inlineStr">
@@ -8113,6 +8221,11 @@
 Готовые цифры, которые можно применить уже завтра: что ставить в прайс, сколько съёмок брать и где проходит ваша нижняя граница.</t>
         </is>
       </c>
+      <c r="H263" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -8137,6 +8250,11 @@
           <t>Готовые цифры, которые можно применить уже завтра: что ставить в прайс, сколько съёмок брать и где проходит ваша нижняя граница.</t>
         </is>
       </c>
+      <c r="H265" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -8161,6 +8279,11 @@
           <t>Поблагодарить и скачать</t>
         </is>
       </c>
+      <c r="H267" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -8185,6 +8308,11 @@
           <t>Что вы узнаете из отчёта</t>
         </is>
       </c>
+      <c r="H269" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -8209,6 +8337,11 @@
           <t>Три вещи, которые меняют разговор о цене: понятный план на месяц, обоснованные скидки и граница, ниже которой нельзя.</t>
         </is>
       </c>
+      <c r="H271" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -8233,6 +8366,11 @@
           <t>Детальный графикна месяц</t>
         </is>
       </c>
+      <c r="H273" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -8257,6 +8395,11 @@
           <t>Сколько съёмок брать и как расставить их по дням, чтобы успевать обрабатывать и не выгорать</t>
         </is>
       </c>
+      <c r="H275" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -8281,6 +8424,11 @@
           <t>Скидкиза объём</t>
         </is>
       </c>
+      <c r="H277" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -8305,6 +8453,11 @@
           <t>Сколько уступить постоянному клиенту за длинную съёмку — за счёт накладных, а не вашего дохода</t>
         </is>
       </c>
+      <c r="H279" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -8329,6 +8482,11 @@
           <t>Минимальнаяцена часа</t>
         </is>
       </c>
+      <c r="H281" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -8353,6 +8511,11 @@
           <t>Точка безубыточности: ниже неё вы работаете себе в убыток. Спокойный ответ на просьбу о скидке</t>
         </is>
       </c>
+      <c r="H283" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -8377,6 +8540,11 @@
           <t>Зачем мы это сделали</t>
         </is>
       </c>
+      <c r="H285" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -8401,6 +8569,11 @@
           <t>Мы сами работаем на себя и знаем, как это бывает: берёшь заказ, вроде бы неплохие деньги, а к концу месяца их нет. Потому что за кадром остались часы обработки, переписка, продвижение и техника, которая изнашивается. Этот калькулятор считает то, что обычно не считают, — и показывает честную цену вашего времени.</t>
         </is>
       </c>
+      <c r="H287" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -8425,6 +8598,11 @@
           <t>Что даёт ваша поддержка</t>
         </is>
       </c>
+      <c r="H289" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -8449,6 +8627,11 @@
           <t>Калькулятор бесплатный и таким останется. Каждая оплата для нас — сигнал, что он действительно нужен и мы делаем полезное дело. Она же защищает сервис от ботов и даёт возможность развивать его дальше: добавлять расчёты, форматы и профессии. Спасибо, что поддерживаете.</t>
         </is>
       </c>
+      <c r="H291" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -8473,6 +8656,11 @@
           <t>Расскажите, что вам нужно ещё</t>
         </is>
       </c>
+      <c r="H293" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="27" t="inlineStr">
@@ -8490,6 +8678,11 @@
           <t>Мы только начинаем и хотим делать то, что действительно пригодится. Отметьте сердечком, какое направление доработать в первую очередь — ваш совет решает.</t>
         </is>
       </c>
+      <c r="H294" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -8650,6 +8843,11 @@
           <t>Отправить</t>
         </is>
       </c>
+      <c r="H304" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="27" t="inlineStr">
@@ -8715,6 +8913,11 @@
           <t>Куда уходит каждый час</t>
         </is>
       </c>
+      <c r="H309" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -8739,6 +8942,11 @@
           <t>Сколько нужно брать, сколько берёте сейчас и минимум без убытка</t>
         </is>
       </c>
+      <c r="H311" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -8763,6 +8971,11 @@
           <t>За какие роли вы это заработали</t>
         </is>
       </c>
+      <c r="H313" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -8787,6 +9000,11 @@
           <t>Фотографом вы работаете меньше всего — основное время уходит на остальное</t>
         </is>
       </c>
+      <c r="H315" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -8812,6 +9030,11 @@
 Часов на проект₽ в год₽ с часа съёмки</t>
         </is>
       </c>
+      <c r="H317" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="27" t="inlineStr">
@@ -8829,6 +9052,11 @@
           <t>Часов в год</t>
         </is>
       </c>
+      <c r="H318" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="27" t="inlineStr">
@@ -8846,6 +9074,11 @@
           <t>Часов на проект</t>
         </is>
       </c>
+      <c r="H319" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -8870,6 +9103,11 @@
           <t>Что это значит</t>
         </is>
       </c>
+      <c r="H321" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="27" t="inlineStr">
@@ -8887,6 +9125,11 @@
           <t>Сетка цен по объёму</t>
         </is>
       </c>
+      <c r="H322" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -8909,6 +9152,11 @@
       <c r="C324" s="113" t="inlineStr">
         <is>
           <t>Чем длиннее съёмка, тем дешевле час — но не за счёт вашего дохода, а за счёт накладных</t>
+        </is>
+      </c>
+      <c r="H324" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -9014,6 +9262,11 @@
           <t>Ваша неделя</t>
         </is>
       </c>
+      <c r="H331" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
@@ -9038,6 +9291,11 @@
           <t>Пять рабочих дней, с 10:00 до 19:00. Каждый квадрат — один час</t>
         </is>
       </c>
+      <c r="H333" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок предварительного отчёта убран из анкеты 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="C334" s="229" t="n"/>
@@ -9065,6 +9323,11 @@
           <t>Цена по вашей реферальной ссылке — для тех, кто пришёл от друга или из нашего блога</t>
         </is>
       </c>
+      <c r="H336" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="27" t="inlineStr">
@@ -9082,6 +9345,11 @@
           <t>Хотите получать рассылку?</t>
         </is>
       </c>
+      <c r="H337" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="27" t="inlineStr">
@@ -9099,6 +9367,11 @@
           <t>Напишем, когда выйдет то, что вы отметили. Без спама, отписка в один клик.</t>
         </is>
       </c>
+      <c r="H338" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="27" t="inlineStr">
@@ -9116,6 +9389,11 @@
           <t>Подписаться</t>
         </is>
       </c>
+      <c r="H339" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="27" t="inlineStr">
@@ -9133,6 +9411,11 @@
           <t>Готово! Спасибо, что остаётесь с нами.</t>
         </is>
       </c>
+      <c r="H340" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="27" t="inlineStr">
@@ -9177,6 +9460,11 @@
           <t>счетикс</t>
         </is>
       </c>
+      <c r="H344" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: слово «счетикс» в знаке выводится без ключа — как в отчёте, 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="27" t="inlineStr">
@@ -9211,6 +9499,11 @@
           <t>Изменить введённые данные</t>
         </is>
       </c>
+      <c r="H346" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="27" t="inlineStr">
@@ -9247,7 +9540,7 @@
       </c>
       <c r="B350" s="112" t="inlineStr">
         <is>
-          <t>Полный отчёт</t>
+          <t>Форма и отчёт · шапка</t>
         </is>
       </c>
       <c r="C350" s="113" t="inlineStr">
@@ -9264,12 +9557,12 @@
       </c>
       <c r="B351" s="112" t="inlineStr">
         <is>
-          <t>Полный отчёт</t>
+          <t>Форма и отчёт · шапка</t>
         </is>
       </c>
       <c r="C351" s="113" t="inlineStr">
         <is>
-          <t>Быть независимым автором не значит работать больше, чем в найме, и постоянно уходить в минус.</t>
+          <t>Создано фотографами для фотографов на основе реального опыта.</t>
         </is>
       </c>
     </row>
@@ -11776,6 +12069,11 @@
           <t>Сколько обработанных кадров вы отдаёте с одного часа съёмки?</t>
         </is>
       </c>
+      <c r="H493" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: блок 04 разбит на пять карточек, вопросы стали заголовками — 10.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="27" t="inlineStr">
@@ -11826,6 +12124,11 @@
         <is>
           <t>Что ещё внутри
 Полная раскладка часа.</t>
+        </is>
+      </c>
+      <c r="H496" s="297" t="inlineStr">
+        <is>
+          <t>УДАЛЕНО из HTML: перенесено из анкеты в части/предварительный_отчёт.html 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12633,7 @@
       </c>
       <c r="B517" s="112" t="inlineStr">
         <is>
-          <t>Форма · шапка</t>
+          <t>Форма и отчёт · логотип</t>
         </is>
       </c>
       <c r="C517" s="113" t="inlineStr">
@@ -13486,12 +13789,12 @@
       </c>
       <c r="B585" s="112" t="inlineStr">
         <is>
-          <t>Полный отчёт · шапка</t>
+          <t>Форма и отчёт · шапка</t>
         </is>
       </c>
       <c r="C585" s="113" t="inlineStr">
         <is>
-          <t>Мы оцифровали ваше творчество и превратили его в точную математическую модель, которая возвращает ценность каждому часу вашего таланта, времени и опыта — и защищает ваш доход от скрытых издержек и работы себе в убыток.</t>
+          <t>Быть независимым автором не значит работать больше, чем в найме, и постоянно уходить в минус.</t>
         </is>
       </c>
     </row>
@@ -14514,6 +14817,57 @@
       <c r="C646" t="inlineStr">
         <is>
           <t>Запас на скидку не заложен. Если хотите иметь возможность сформировать программу лояльности и давать скидки своим клиентам не только за объём — вернитесь в анкету и включите «Запас на скидку».</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>rthx_05</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Отчёт · пояснение под кнопкой «Поблагодарить проект»</t>
+        </is>
+      </c>
+      <c r="C647" s="229" t="inlineStr">
+        <is>
+          <t>Так мы будем знать, что сервис вам нужен, и сможем развивать его и сохранять бесплатным для всех специалистов креативной индустрии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>rthx_04</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Отчёт · баннер «Поблагодарить проект», описание</t>
+        </is>
+      </c>
+      <c r="C648" s="229" t="inlineStr">
+        <is>
+          <t>Так мы будем знать, что сервис вам нужен, и сможем развивать его и сохранять бесплатным для всех специалистов креативной индустрии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>rfc_01</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Форма и отчёт · подвал, реквизиты</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>ООО «Центр маркетинговых услуг Гет Маркетинг» © 2026</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22696,6 +23050,3831 @@
       <c r="B102" s="229" t="inlineStr">
         <is>
           <t>REFD и PHR_REF вынесены выше отрисовки блоков: легенда блока 01 строится раньше справочника и без этого ссылок не получала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ВТОРОЙ ЭКРАН И КНОПКИ БЛАГОДАРНОСТИ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Экран 2 — рабочий месяц</t>
+        </is>
+      </c>
+      <c r="B105" s="229" t="inlineStr">
+        <is>
+          <t>Всё переведено в месяц: год человек не чувствует, месяц планирует. Один заголовок «Ваш рабочий месяц» и три рамки: съёмок в месяц, часов на работу с заказом (обработка + клиент), продвижение и прочее. Рамки прозрачные, только контур. Проверка: 18+72+56=146 ч = всё рабочее время за месяц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Гамма и фон</t>
+        </is>
+      </c>
+      <c r="B106" s="229" t="inlineStr">
+        <is>
+          <t>Морская волна #176B77 → #58B1B9 — взята из карточки «Ставка в ноль» блока «Четыре цифры» (.fct.b). Ближе к зелёному, чем прежний синий. Фоновый рисунок — часы вместо фотоаппарата, прозрачность 13%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Кнопка благодарности</t>
+        </is>
+      </c>
+      <c r="B107" s="229" t="inlineStr">
+        <is>
+          <t>.thxb — форма от .savebtn (ширина 100%, высота 72px, кегль 17px, радиус, отступы 0/30, зазор 11px), оформление от плашек блока 08 (.cn.s1..s3): инста-градиент заливкой --c-ig-1 → --c-ig-2 → --c-ig-4, белый текст и сердце, круг-блик :before в углу, тень. Рамки нет. При наведении яркость +6%. Мест три: под кнопкой PDF, между блоками 04 и 05, баннер перед справочником. Из шапки убрана 10.08.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Баннер</t>
+        </is>
+      </c>
+      <c r="B108" s="229" t="inlineStr">
+        <is>
+          <t>.cta.thx — тот же приём, что «30 сценариев», гамма тёплая (--c-a-700 → --c-a-500), декор-сердце вместо стопки карточек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>THANKS_URL</t>
+        </is>
+      </c>
+      <c r="B109" s="229" t="inlineStr">
+        <is>
+          <t>Адрес задаётся одной переменной в скрипте отчёта, подставляется во все кнопки разом. Сейчас заглушка #thanks. Если адрес внешний — ссылки автоматически открываются в новой вкладке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>собрать.py</t>
+        </is>
+      </c>
+      <c r="B110" s="229" t="inlineStr">
+        <is>
+          <t>Ожидаемое число прямых детей .wp: 19 → 22 (добавились две плашки с кнопками и баннер).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ССЫЛКИ И КНОПКИ — единый вид, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ссылка на справочник</t>
+        </is>
+      </c>
+      <c r="B113" s="229" t="inlineStr">
+        <is>
+          <t>.refl — цветом НЕ выделяется: color:inherit, font:inherit. Наследует кегль, начертание и цвет того описания, вместо которого стоит. Обозначена только подчёркиванием currentColor. Текст короткий: «п. 22 Справочника», без «Подробнее в».</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ссылки в памятке</t>
+        </is>
+      </c>
+      <c r="B114" s="229" t="inlineStr">
+        <is>
+          <t>Блок 04 и другие .pmknote: было своё оформление (цвет --c-fns-2, полужирный) — приведено к тому же правилу, что .refl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Кнопки и баннер</t>
+        </is>
+      </c>
+      <c r="B115" s="229" t="inlineStr">
+        <is>
+          <t>Единая гамма: инста-градиент --c-ig-1 → --c-ig-2 → --c-ig-4. Баннер был тёплый (--c-a-700), переведён в ту же гамму. Декор везде одинаковый: круг-блик плюс сердечки. На кнопках два сердца (.thxd справа 56px, .thxd2 слева 34px), на баннере два круга и два сердца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>БАННЕР «30 СЦЕНАРИЕВ» ВЫНЕСЕН, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Куда</t>
+        </is>
+      </c>
+      <c r="B118" s="229" t="inlineStr">
+        <is>
+          <t>части/09_баннер_сценарии.html — полноценная страница, дизайн сохранён без изменений. В собрать.py 22 → 21 блока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Важно</t>
+        </is>
+      </c>
+      <c r="B119" s="229" t="inlineStr">
+        <is>
+          <t>Стили .cta ОСТАЛИСЬ в каркасе: их наследует баннер благодарности .cta.thx. Вынесена только разметка. При первой попытке я скопировала правила в каркас поверх существующих — получились дубли, убраны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Пояснение под кнопкой</t>
+        </is>
+      </c>
+      <c r="B120" s="229" t="inlineStr">
+        <is>
+          <t>.thxn — абзац под кнопкой «Поблагодарить проект» (той, что под сохранением в PDF). Лежит ВНУТРИ .thxbar, иначе становится прямым ребёнком .wp и ломает проверку структуры. Ширина 720px, кегль 13, по центру, цвет --c-gr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>БАННЕР «30 СЦЕНАРИЕВ» — СКРЫТ, НЕ УДАЛЁН, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Как сделано</t>
+        </is>
+      </c>
+      <c r="B123" s="229" t="inlineStr">
+        <is>
+          <t>Баннер остаётся в каркасе с классом .hide (display:none!important). Чтобы вернуть — снять класс, ничего искать не нужно. Копия для просмотра: части/09_баннер_сценарии.html.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Что было сломано</t>
+        </is>
+      </c>
+      <c r="B124" s="229" t="inlineStr">
+        <is>
+          <t>При первом выносе я удалила разметку и вырезала правила .cta. Баннер благодарности .cta.thx наследует .cta, поэтому потерял заливку, радиус 22px и отступы 40/44 — остался только мобильный вариант padding:30px 24px. Восстановлено сверкой правило-в-правило с report_prev405.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Правило .hide</t>
+        </is>
+      </c>
+      <c r="B125" s="229" t="inlineStr">
+        <is>
+          <t>Общее: элементы скрываются классом, а не удаляются. Так проще вернуть и видно в разметке, что элемент есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ВЕРХНЕЕ МЕНЮ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B128" s="229" t="inlineStr">
+        <is>
+          <t>Логотип вынесен из шапки в отдельную строку .topbar. Строка липкая: position:sticky, полупрозрачный белый фон с размытием 10px. Высота строки 66px — логотип 62px размещается свободно. Отступ до заголовка «Юнит-экономика» 34px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Прилипание</t>
+        </is>
+      </c>
+      <c r="B129" s="229" t="inlineStr">
+        <is>
+          <t>Класс .stuck вешается через IntersectionObserver: сторож в 1px над полосой пропал из виду — значит прилипла, появляются черта снизу и мягкая тень. Слушать прокрутку не нужно, браузер делает сам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Кнопки меню</t>
+        </is>
+      </c>
+      <c r="B130" s="229" t="inlineStr">
+        <is>
+          <t>Слева логотип, справа в один ряд: текстовая «Редактировать данные» (без плашки, с тонким подчёркиванием) и сердце. У сердца подпись «Поблагодарить проект» раскрывается при наведении через max-width. На узких экранах подпись скрыта, остаётся значок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Адреса</t>
+        </is>
+      </c>
+      <c r="B131" s="229" t="inlineStr">
+        <is>
+          <t>EDIT_URL=calc.html — отдельная переменная рядом с THANKS_URL. При печати полоса становится обычной, без фона и тени.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ПЛАВАЮЩАЯ ПАНЕЛЬ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Что изменилось</t>
+        </is>
+      </c>
+      <c r="B134" s="229" t="inlineStr">
+        <is>
+          <t>Логотип вернулся в шапку. Липкая полоса во всю ширину заменена на компактную плавающую панель справа сверху. Логотипа в ней нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Появление</t>
+        </is>
+      </c>
+      <c r="B135" s="229" t="inlineStr">
+        <is>
+          <t>Скрыта по умолчанию (opacity:0, visibility:hidden). Всплывает после 500 px прокрутки, плавно съезжая сверху. При обратной прокрутке прячется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Подложка</t>
+        </is>
+      </c>
+      <c r="B136" s="229" t="inlineStr">
+        <is>
+          <t>Полупрозрачная белая .62 с размытием 14px и насыщением 140%. Углы как у блоков — var(--r). Отступы 12/18, зазор 14. Панель по ЦЕНТРУ экрана: left:50% + translateX(-50%), не прижата к краю.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Содержимое</t>
+        </is>
+      </c>
+      <c r="B137" s="229" t="inlineStr">
+        <is>
+          <t>Текстовая «Редактировать данные» → calc.html, значок «Поделиться», значок сердца. Разворачивающаяся подпись убрана: у обоих значков всплывающая подсказка через :after с data-tip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Поделиться</t>
+        </is>
+      </c>
+      <c r="B138" s="229" t="inlineStr">
+        <is>
+          <t>navigator.share, где поддерживается (телефоны). Иначе ссылка копируется в буфер и подсказка на 1,8 с меняется на «Ссылка скопирована».</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Панель — правки 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B139" s="229" t="inlineStr">
+        <is>
+          <t>1) Панель центрирована по горизонтали. 2) Кнопка «Редактировать данные» выделяется при наведении так же, как значки: подложка --c-bg и радиус 11px вместо подчёркивания. 3) Всплывающие подсказки оформлены как .segtip (подсказка на диаграмме блока 01): белый фон, рамка --c-ln, радиус 12px, тень 0 8px 28px, цвет --c-ink. Сверено посвойствно — совпадает полностью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ВЕРХНЕЕ МЕНЮ — окончательный вид, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Устройство</t>
+        </is>
+      </c>
+      <c r="B142" s="229" t="inlineStr">
+        <is>
+          <t>.tbar — липкая строка над шапкой: логотип слева, кнопки справа (Редактировать данные · Поделиться · сердце). Логотип стоит на прежней высоте, как и был.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Без подложки</t>
+        </is>
+      </c>
+      <c r="B143" s="229" t="inlineStr">
+        <is>
+          <t>Фон меню = var(--c-bg), тот же, что у страницы: меню читается как её продолжение. Размытия, тени и полупрозрачности нет. Когда меню прилипает, снизу проступает тонкая черта --c-ln, чтобы отделиться от содержимого.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Кнопки</t>
+        </is>
+      </c>
+      <c r="B144" s="229" t="inlineStr">
+        <is>
+          <t>Текстовая и значки выделяются одинаково: белая подложка --c-white и радиус 11px при наведении. Подсказки как .segtip блока 01 — белый фон, рамка --c-ln, радиус 12, та же тень.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Отличие от прежнего</t>
+        </is>
+      </c>
+      <c r="B145" s="229" t="inlineStr">
+        <is>
+          <t>Плавающая панель по центру с полупрозрачной подложкой и порогом 500px отменена. Меню видно всегда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ПЕРЕЛИВАНИЕ, КНОПКА СКАЧИВАНИЯ, РЕКВИЗИТЫ — 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Анимация</t>
+        </is>
+      </c>
+      <c r="B148" s="229" t="inlineStr">
+        <is>
+          <t>@keyframes thxSheen — светлая полоса под углом 105° проходит по кнопке слева направо за 55% цикла, остальное время пауза. На кнопках .thxb цикл 5,5 с, на баннере .cta.thx 7 с и полоса бледнее. Идёт постоянно, но мягко. При системной настройке «уменьшить движение» гасится — правило стоит ПОСЛЕ обычного, иначе не сработает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Кнопка скачивания</t>
+        </is>
+      </c>
+      <c r="B149" s="229" t="inlineStr">
+        <is>
+          <t>#dlBtn в меню, перед «Поделиться». Значок стрелки вниз, как у .savebtn. Запускает ту же печать в PDF с подстановкой имени файла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Реквизиты</t>
+        </is>
+      </c>
+      <c r="B150" s="229" t="inlineStr">
+        <is>
+          <t>.fcop под знаком в подвале: ООО «Центр маркетинговых услуг Гет Маркетинг» © 2026. Кегль 11,5, цвет --c-gr2. Подвал перестроен в столбик. Ключ текста rfc_01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>МЕНЮ, ПЛАШКА И ВРАЩЕНИЕ ГРАДИЕНТА — 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Меню .tbar</t>
+        </is>
+      </c>
+      <c r="B153" s="229" t="inlineStr">
+        <is>
+          <t>Обычное, НЕ липкое: прокручивается вместе со страницей. Логотип справа, кнопки слева (Редактировать · Скачать · Поделиться · сердце). Фон как у страницы, подложки нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Плашка .fbar</t>
+        </is>
+      </c>
+      <c r="B154" s="229" t="inlineStr">
+        <is>
+          <t>Отдельный элемент. Появляется после 500 px прокрутки, висит по центру сверху (left:50% + translateX). Логотипа нет, только действия. Полупрозрачная подложка с размытием, углы var(--r). Кнопки продублированы с суффиксом 2, обработчики вешаются на пары через forEach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Анимация переливания — ОТМЕНЕНА 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B155" s="229" t="inlineStr">
+        <is>
+          <t>Пробовали два варианта: бегущий блик и вращение градиента (линейный, затем конический через @property). Оба выглядели некрасиво: у линейного поворот на 180° даёт зеркальную картинку, и оборот читался как два прохода. По решению заказчика анимация убрана полностью — на кнопках .thxb и баннере .cta.thx обычная неподвижная заливка linear-gradient(140deg, --c-ig-1 → --c-ig-2 42% → --c-ig-4). Удалены: @property --ang, @keyframes thxSpin, conic-gradient, правило prefers-reduced-motion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Справочник .pmknote — без подложки, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B156" s="229" t="inlineStr">
+        <is>
+          <t>Убраны фон --c-surf, скругление 16px и рамка. Фон теперь общий, как у страницы и меню. Боковые отступы сняты: текст выравнивается по общей колонке, padding 22px 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Отступ меню сверху, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B157" s="229" t="inlineStr">
+        <is>
+          <t>Меню поднято к верхнему краю: над ним 28 px. Считается как отступ страницы 32 − собственный margin-top −12 + padding-top 8. Не вплотную, но и не провисает. На узких экранах: 32 − 8 + 6 = 30 px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ПОЯВЛЕНИЕ ДИАГРАММ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B160" s="229" t="inlineStr">
+        <is>
+          <t>Перенесено из анкеты: диаграмма оживает, когда доезжает до экрана. Охвачены все 10: кольцо блока 01, две легенды-полосы блока 01, сетка недели блока 02, кольцо фонда и две группы полос блока 03, три кольца сценариев блока 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Кольцевые диаграммы — посекторное появление</t>
+        </is>
+      </c>
+      <c r="B161" s="229" t="inlineStr">
+        <is>
+          <t>Перенесено полностью из анкеты: каждый сектор выезжает отдельно, с задержкой 90 мс между соседними. Кольцо фонда блока 03 нарисовано обводкой — там тот же приём, что в анкете: &lt;animate&gt; по stroke-dasharray прямо на circle. Кольца блоков 01 и 05 — секторы-path, к ним stroke-dasharray неприменим: для каждого сектора создаётся МАСКА с дугой по средней линии кольца, и растёт обводка внутри маски, открывая сектор от начала к концу. Всего 20 секторов в 5 кольцах, id масок уникальны (счётчик donut._n). Запуск через beginElement() по наблюдателю, begin="indefinite". Подписи процентов проступают через .55 с, когда секторы уже на местах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Полосы</t>
+        </is>
+      </c>
+      <c r="B162" s="229" t="inlineStr">
+        <is>
+          <t>Ширина вынесена в переменную --w, сама width обнуляется до появления и возвращается к --w с переходом .9s. Иначе анимации нечего было бы восстанавливать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Наблюдатель</t>
+        </is>
+      </c>
+      <c r="B163" s="229" t="inlineStr">
+        <is>
+          <t>IntersectionObserver, порог .18 и rootMargin −8% снизу. Срабатывает ОДИН раз (unobserve), при обратной прокрутке диаграмма не схлопывается. Без поддержки наблюдателя всё показывается сразу. При печати и «уменьшить движение» анимация отключена, значения конечные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Шапка отчёта — во всю ширину, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B164" s="229" t="inlineStr">
+        <is>
+          <t>Снято max-width:660px у .sub — оно рвало подзаголовок посередине строки. Убран флекс на две колонки у .hdr: логотип теперь в меню, делить ширину не с кем. Заголовок, подзаголовок и описание занимают всю колонку 1080px. Заодно убрано мобильное правило column-reverse — оно относилось к паре «текст + логотип».</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>КНОПКА ИСПРАВЛЕНИЯ В ПРЕДУПРЕЖДЕНИЯХ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B167" s="229" t="inlineStr">
+        <is>
+          <t>В плашках .note.warn внутри легенды блока 01 появилась кнопка .lgwb: ведёт прямо к нужному полю анкеты, человек исправляет сразу, не разыскивая вопрос. «Заложить фонд развития» → calc.html#fund_on, «Заложить запас на скидку» → calc.html#disc_on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Как устроено</t>
+        </is>
+      </c>
+      <c r="B168" s="229" t="inlineStr">
+        <is>
+          <t>Блок 01: массив ZWA[i] = [id поля, надпись] рядом с ZW[i]. Блок 03 (#zapbox, резерв не заложен): кнопка дописана прямо в innerHTML уведомления. Всего три кнопки: фонд развития (блок 01), запас на скидку (блок 01), резерв на скидку (блок 03) — последние две ведут на одно поле disc_on. Адрес анкеты из общей переменной EDIT_URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="B169" s="229" t="inlineStr">
+        <is>
+          <t>Кнопка .lgwb стоит ОТДЕЛЬНОЙ строкой под текстом плашки: display:table прижимает её по содержимому и переносит с новой строки (inline-flex вставлял её в конец последнего абзаца). Отступ сверху 12px. Гамма предупреждения: белый фон, рамка --c-a-300, текст --c-a-800. Стрелки перед надписью нет. При печати скрыта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+      <c r="B170" s="229" t="inlineStr">
+        <is>
+          <t>«Отложите в фонд развития» → «Отложите запас средств в фонд развития».</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ПРЕДВАРИТЕЛЬНЫЙ ОТЧЁТ ВЫНЕСЕН ИЗ АНКЕТЫ, 10.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Куда</t>
+        </is>
+      </c>
+      <c r="B173" s="229" t="inlineStr">
+        <is>
+          <t>части/предварительный_отчёт.html — самодостаточная страница: стили и скрипт анкеты внутри, можно открыть и посмотреть. Перенесено всё после кнопки «Рассчитать стоимость часа»: индикатор #ld, весь результат #res (7 карточек, 6 заголовков, размытие lockwrap и блок оплаты paywall), полоса лимитов #limBar. Всего 224 строки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Дословность</t>
+        </is>
+      </c>
+      <c r="B174" s="229" t="inlineStr">
+        <is>
+          <t>Проверено посимвольно: 80 210 знаков до и после, совпадение полное. Баланс тегов нулевой в обоих файлах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Что пришлось поправить</t>
+        </is>
+      </c>
+      <c r="B175" s="229" t="inlineStr">
+        <is>
+          <t>Скрипт анкеты обращался к кнопкам отчёта напрямую ($(buy), $(dlpdf)) и падал — обращения защищены проверкой. В вынесенном файле зеркальная проблема: скрипт зовёт поля анкеты, которых там нет, — добавлена заглушка getElementById, отдающая невидимую пустышку. Тот же приём, что в файлах блоков.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>calc.html</t>
+        </is>
+      </c>
+      <c r="B176" s="229" t="inlineStr">
+        <is>
+          <t>234 812 → 154 600 байт. Осталась только анкета: 14 карточек и кнопка расчёта. Загружается без ошибок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Предварительный отчёт — показ в вынесенном файле, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B177" s="229" t="inlineStr">
+        <is>
+          <t>Была видна одна плашка: #res скрыт до нажатия «Рассчитать», а кнопка осталась в анкете; плюс пять карточек лежат в .lockwrap ЗА пределами #res (так в исходнике) и прятались paywall-логикой. Добавлен блок стилей ТОЛЬКО для этого файла: #res показан, размытие и лимит высоты сняты, .paywall скрыт. Расчёт запускается изнутри замыкания — снаружи render/calc не видны. Значения по умолчанию собраны из самой анкеты (24 поля), поэтому цифры живые: ставка 8 959 ₽. Разметка блока между метками не тронута.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>РАЗБОР ПРЕДВАРИТЕЛЬНОГО ОТЧЁТА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B179" s="229" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Что осталось в анкете</t>
+        </is>
+      </c>
+      <c r="B180" s="229" t="inlineStr">
+        <is>
+          <t>Сама анкета, кнопка «Рассчитать стоимость часа» и анимация расчёта. Больше в calc.html ничего нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Анимация расчёта</t>
+        </is>
+      </c>
+      <c r="B181" s="229" t="inlineStr">
+        <is>
+          <t>Была карточкой в потоке страницы, стала слоем во весь экран: #ld — position:fixed;inset:0, внутри карточка .ldin по центру. Подложка как у полосы лимитов — полупрозрачный фон и размытие. Кольцо, проценты и подписи этапов не тронуты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Что происходит после 100%</t>
+        </is>
+      </c>
+      <c r="B182" s="229" t="inlineStr">
+        <is>
+          <t>Результат кладётся в localStorage (saveReport) и в phc_state (saveState), затем переход на report.html. Раньше отчёт разворачивался прямо в анкете.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Перенесено в части/предварительный_отчёт.html</t>
+        </is>
+      </c>
+      <c r="B183" s="229" t="inlineStr">
+        <is>
+          <t>Три блока подряд: «Куда уходит каждый час съёмки», «Сравните со своим текущим доходом» и «Скачать детальный отчёт» целиком — с ценой, преимуществами, кнопками, опросом, подпиской, строкой «Оплатили, но отчёт не открылся?» и логотипом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Удалено совсем</t>
+        </is>
+      </c>
+      <c r="B184" s="229" t="inlineStr">
+        <is>
+          <t>Главный экран со ставкой, «Спасибо за поддержку» с кнопкой PDF и пять карточек размытого превью: блоки 17, 18, 19, 19b и 20. Полоса лимитов #limBar осталась в анкете — она работает во время заполнения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Что убрано из скрипта</t>
+        </is>
+      </c>
+      <c r="B185" s="229" t="inlineStr">
+        <is>
+          <t>render, donut, parts, visIdx, массивы CO и LB, PWL и fillPW, isPaid, unlock, lockOn, setPrice с ценами, обработчики кнопок оплаты и PDF, опрос и подписка, goEdit, ветка возврата из оплаты. Остались calc, recalc, лимиты, saveReport, saveState, restoreState.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="B186" s="229" t="inlineStr">
+        <is>
+          <t>calc.html: 249 268 → 106 675 байт. Разметка и скрипт сходятся: баланс тегов ноль, ни одного обращения к несуществующему id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ВТОРАЯ КНОПКА «ПОБЛАГОДАРИТЬ ПРОЕКТ» ПЕРЕЕХАЛА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B188" s="229" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B189" s="229" t="inlineStr">
+        <is>
+          <t>Стояла между блоками 04 и 05 — после таблицы налоговых режимов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B190" s="229" t="inlineStr">
+        <is>
+          <t>Стоит между блоками 03 и 04 — сразу после программы лояльности, перед «Ваш идеальный налоговый режим».</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Что изменилось в вёрстке</t>
+        </is>
+      </c>
+      <c r="B191" s="229" t="inlineStr">
+        <is>
+          <t>Только положение строки .thxbar в каркасе. Разметка, классы и текст не тронуты, оформление сверка с прошлой сборкой не показала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ШАПКА И ПОДВАЛ АНКЕТЫ ПРИВЕДЕНЫ К ОТЧЁТУ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B193" s="229" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Образец</t>
+        </is>
+      </c>
+      <c r="B194" s="229" t="inlineStr">
+        <is>
+          <t>report.html — самый проработанный файл. Правила скопированы дословно, сверка селекторов показала полное совпадение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Шапка</t>
+        </is>
+      </c>
+      <c r="B195" s="229" t="inlineStr">
+        <is>
+          <t>Заголовок и обе строки под ним теперь общие: rh_01, rh_02, rh_03. Ширина не ограничена, .htx без верхнего отступа, на узком экране заголовок 26 px. В анкете нет верхнего меню с кнопками, плавающей плашки, логотипа справа и строки с датой расчёта — даты в анкете быть не может, расчёта ещё нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Подвал</t>
+        </is>
+      </c>
+      <c r="B196" s="229" t="inlineStr">
+        <is>
+          <t>Взят из отчёта целиком: знак с растянутой подписью «твоя юнит-экономика» и под ним реквизиты .fcop. Был маленький значок со словом «счетикс» в одну строку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Что вышло из употребления</t>
+        </is>
+      </c>
+      <c r="B197" s="229" t="inlineStr">
+        <is>
+          <t>Ключи h1_01, sub_01 и bt_01 больше не в вёрстке — помечены красным в 09_Тексты. Правила .brand, .lt и .lx из анкеты убраны: логотип в шапке не выводится.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ЗНАК В ШАПКЕ АНКЕТЫ ВОЗВРАЩЁН, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B199" s="229" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Что было не так</t>
+        </is>
+      </c>
+      <c r="B200" s="229" t="inlineStr">
+        <is>
+          <t>При выравнивании шапки по отчёту знак из анкеты убрали. Он должен стоять везде и выглядеть одинаково.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Как сделано</t>
+        </is>
+      </c>
+      <c r="B201" s="229" t="inlineStr">
+        <is>
+          <t>Перенесена строка .tbar из отчёта вместе со знаком .brand. Разметка знака скопирована посимвольно — совпадение полное, и в шапке, и в подвале. Правила .tbar, .brand и всех вложенных совпадают с отчётом, включая мобильный и печатный медиазапросы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Единственное отличие</t>
+        </is>
+      </c>
+      <c r="B202" s="229" t="inlineStr">
+        <is>
+          <t>В отчёте знак прижат вправо кнопками слева. В анкете кнопок нет, поэтому у .tbar добавлено justify-content:flex-end — иначе знак уехал бы к левому краю. Место, размеры, цвета и тональность те же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ЗАПАС ПРОЧНОСТИ РАЗДЕЛЁН НА ДВА БЛОКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B204" s="229" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B205" s="229" t="inlineStr">
+        <is>
+          <t>Один блок 15 «Запас прочности» с общим подзаголовком, внутри две рамки и один флажок «не учитывать этот блок в расчёте» на обе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B206" s="229" t="inlineStr">
+        <is>
+          <t>Блок 15 «Фонд развития» и блок 16 «Запас на скидку», у каждого свой заголовок и подзаголовок. Внутри — прежняя рамка .zap со своей галочкой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Флажок убран</t>
+        </is>
+      </c>
+      <c r="B207" s="229" t="inlineStr">
+        <is>
+          <t>«Не учитывать этот блок в расчёте» удалён из обоих: галочка внутри рамки и так работает на включение, два переключателя об одном и том же мешали друг другу. В расчёте снята проверка EXC[Form016] — теперь fundP и discP зависят только от своих галочек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Заливка ползунка</t>
+        </is>
+      </c>
+      <c r="B208" s="229" t="inlineStr">
+        <is>
+          <t>Дорожка фонда развития слева от бегунка зеленеет. Доля считается в JS и кладётся в переменную --zp, дорожка залита линейным градиентом с жёсткой границей: слева c-g-350 → c-g-500, справа c-ln. Пока галочка снята, рядом стоит 0% и дорожка пустая — иначе цифра и полоса спорят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Проверка расчёта</t>
+        </is>
+      </c>
+      <c r="B209" s="229" t="inlineStr">
+        <is>
+          <t>Сверены все 60 полей результата до и после правки: расхождений нет, ставка та же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>КНОПКА РАСЧЁТА И ЭКРАН РАСЧЁТА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B211" s="229" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Образец</t>
+        </is>
+      </c>
+      <c r="B212" s="229" t="inlineStr">
+        <is>
+          <t>Кнопка «Сохранить отчёт в PDF» (.savebtn) из отчёта — на неё же равняются «Поблагодарить проект» и остальные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Кнопка расчёта</t>
+        </is>
+      </c>
+      <c r="B213" s="229" t="inlineStr">
+        <is>
+          <t>Была зелёная заливка, ширина 420, радиус 16, своя тень. Стала как в отчёте: белая, во всю колонку, высота 72, радиус блока, светлая рамка, общая тень, при наведении зелёная рамка и светло-зелёная подложка. Слева значок, как у всех кнопок отчёта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Отступ до подвала</t>
+        </is>
+      </c>
+      <c r="B214" s="229" t="inlineStr">
+        <is>
+          <t>Кнопка обёрнута в .savebar из отчёта. Снизу 56 px вместо прежних 0 — подвал со знаком и реквизитами опущен, между ними появился воздух.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Экран расчёта</t>
+        </is>
+      </c>
+      <c r="B215" s="229" t="inlineStr">
+        <is>
+          <t>Карточка была 420 px по центру, стала во всю ширину колонки — 1080, как обычный блок, с теми же радиусом и тенью, отступы внутри 72.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Кольцо</t>
+        </is>
+      </c>
+      <c r="B216" s="229" t="inlineStr">
+        <is>
+          <t>Было 78 px, тонкая обводка 7 и длина окружности 207. Стало 200 px, обводка 14, длина 578, заливка градиентом c-g-350 → c-g-700 (оба стопа разные). Проценты 46 px, этап 23 px. Вторым слоем — шесть точек по кругу с затухающей прозрачностью, вращаются 5,5 с; при prefers-reduced-motion вращение снято.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B217" s="229" t="inlineStr">
+        <is>
+          <t>Кольцо проходит полный круг: dashoffset идёт от 578 до нуля. На узком экране кольцо 150 px, проценты 34 px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ИСХОДНАЯ ВЁРСТКА БЛОКА 03 СОХРАНЕНА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B219" s="229" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Где лежит</t>
+        </is>
+      </c>
+      <c r="B220" s="229" t="inlineStr">
+        <is>
+          <t>_архив/исходники/03_блок_скидок_исходный_2026-08-10.html — 223 683 байта. Заведена новая папка «исходники», её назначение описано в КАК_УСТРОЕН_АРХИВ.txt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Почему не в «части»</t>
+        </is>
+      </c>
+      <c r="B221" s="229" t="inlineStr">
+        <is>
+          <t>В «части» лежат рабочие файлы: собрать.py и блок.py берут оттуда разметку между метками БЛОК-НАЧАЛО и БЛОК-КОНЕЦ. Присланный файл — не рабочий, а справочный, у него те же метки и тот же id card06. Оставь его рядом — и однажды он подменит собой текущий блок при сборке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Чем отличается от текущего</t>
+        </is>
+      </c>
+      <c r="B222" s="229" t="inlineStr">
+        <is>
+          <t>Разметка блока: было 1 205 байт, стало 4 873. В исходном нет трёх подблоков «Скидка за объём», «Скидка постоянному клиенту» и «Специальные предложения» — есть только карта скидок и вставка про накладные. Нет ключей rgn_10 … rgn_14, нет id dst, loy, spc, fnd, pgb1-3. Строка-статус была статичной разметкой .dst с двумя вариантами текста, теперь её собирает скрипт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Что в нём есть полезного</t>
+        </is>
+      </c>
+      <c r="B223" s="229" t="inlineStr">
+        <is>
+          <t>49 правил, которых нет в текущем файле: .idc и .idg (карточки), .lad со ступенями, .loyc с подложками, .fnd .fg и .fnf (фонд), .ftop, .mkh. Пригодятся при переносе правок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>КНОПКА РАСЧЁТА — ЗЕЛЁНАЯ СО ЗНАКОМ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B225" s="229" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Что осталось от кнопок отчёта</t>
+        </is>
+      </c>
+      <c r="B226" s="229" t="inlineStr">
+        <is>
+          <t>Форма и размеры: во всю колонку, высота 72, радиус блока, размер и насыщенность надписи, значок слева.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Что своё</t>
+        </is>
+      </c>
+      <c r="B227" s="229" t="inlineStr">
+        <is>
+          <t>Заливка. Это главное действие анкеты, поэтому зелёный градиент шапки отчёта c-g-800 → c-g-500, белая надпись, зелёная тень. При наведении градиент темнеет до c-g-900 → c-g-600, при нажатии утапливается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Фоновый знак</t>
+        </is>
+      </c>
+      <c r="B228" s="229" t="inlineStr">
+        <is>
+          <t>Два ромба «Счетикс» лежат фоном внутри кнопки: крупный слева заходит за край, поменьше справа. Приём и прозрачности взяты у .hdeco — фонового знака в шапке отчёта: .07 и .09. Надпись и значок лежат выше по слою, знак им не мешает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Читаемость</t>
+        </is>
+      </c>
+      <c r="B229" s="229" t="inlineStr">
+        <is>
+          <t>Белый текст на тёмно-зелёном градиенте — та же пара, что в шапке отчёта и на баннере .cta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>БЛОКИРУЮЩИЕ ФЛАЖКИ — КРАСНЫЕ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B230" s="229" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+      <c r="B231" s="229" t="inlineStr">
+        <is>
+          <t>«Не учитывать этот блок в расчёте» выключает часть расчёта. Это не правильный выбор, а изъятие — зелёный галочкой сбивал с толку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B232" s="229" t="inlineStr">
+        <is>
+          <t>У .exc галочка красная, c-r-500. Пока флажок стоит, подпись тоже красная, c-r-700, и полужирная — сразу видно, какие блоки изъяты. Галочки .flag внутри карточек не тронуты: они работают на включение и остаются зелёными.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>СТРАНИЦА ВХОДА index.html, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B234" s="229" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Что это</t>
+        </is>
+      </c>
+      <c r="B235" s="229" t="inlineStr">
+        <is>
+          <t>Четвёртый файл продукта. Первое, что видит человек: один экран без прокрутки — заголовок, три пользы, кнопка. Дальше он проваливается в анкету.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Устройство</t>
+        </is>
+      </c>
+      <c r="B236" s="229" t="inlineStr">
+        <is>
+          <t>Строка со знаком сверху, тёмно-зелёное полотно во весь оставшийся рост, подвал снизу. Полотно — заливка шапки отчёта, развёрнутая по диагонали, плюс четыре фоновых ромба с прозрачностями .06–.10, приём .hdeco из отчёта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Кнопка</t>
+        </is>
+      </c>
+      <c r="B237" s="229" t="inlineStr">
+        <is>
+          <t>Форма от кнопок отчёта: высота 72, радиус блока, значок слева. Здесь белая на зелёном — обратная пара к кнопке анкеты. Значок тот же, что на «Рассчитать стоимость часа».</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Тексты</t>
+        </is>
+      </c>
+      <c r="B238" s="229" t="inlineStr">
+        <is>
+          <t>Три пользы дословно из блока оплаты: «Детальный график на месяц», «Скидки за объём», «Минимальная цена часа». Заголовок и подводка новые. Ключи wh_01, wl_01, wk_01, wa_01-03, wax_01-03, wu_01 — в 09_Тексты пока не заведены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Реферальная ссылка</t>
+        </is>
+      </c>
+      <c r="B239" s="229" t="inlineStr">
+        <is>
+          <t>Метка приходит на index.html и переносится в анкету целиком: строка запроса подставляется в обе ссылки. Без этого цена по реферальной ссылке в блоке оплаты не сработала бы — там isRef() читает ref, utm_source и from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Пропуск</t>
+        </is>
+      </c>
+      <c r="B240" s="229" t="inlineStr">
+        <is>
+          <t>Два пути. Ссылка «Пропустить и считать» слева вверху — разовый обход, метку не ставит. Кнопка «Рассчитать» ставит phc_seen: кто уже начинал, при следующем заходе попадает сразу в анкету. Метка ставится по нажатию, а не при загрузке, иначе закрывший вкладку человек больше не увидел бы страницу. Показ можно навязать: index.html?hello=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B241" s="229" t="inlineStr">
+        <is>
+          <t>Скобки, переменные, медиазапросы, дубли — чисто. Все цвета из палитры. Метка ?ref=blog&amp;utm_source=vk доходит до анкеты, phc_seen ставится по нажатию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ПЕРЕСБОРКА БЛОКОВ АНКЕТЫ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B243" s="229" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Блоков было 16, стало 16</t>
+        </is>
+      </c>
+      <c r="B244" s="229" t="inlineStr">
+        <is>
+          <t>Порядок: 01 доход · 02 налоговый режим · 03 текущая ставка · 04 как устроена работа · 05-13 расходы · 14 форс-мажоры · 15 фонд развития · 16 запас на скидку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Налоговый режим</t>
+        </is>
+      </c>
+      <c r="B245" s="229" t="inlineStr">
+        <is>
+          <t>Блок 02 назывался «Режим и текущая ставка» — вопрос про ставку из него убран, осталось только про режим. Заголовок переименован, ключ h2_02 в книге поправлен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Текущая ставка</t>
+        </is>
+      </c>
+      <c r="B246" s="229" t="inlineStr">
+        <is>
+          <t>Вынесена в отдельный блок 03 с подзаголовком «С ней мы сравним расчётную — чтобы вы увидели разницу в год и в месяц». Вопрос, подсказка и поле перенесены дословно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Блоки 04 и 05 объединены</t>
+        </is>
+      </c>
+      <c r="B247" s="229" t="inlineStr">
+        <is>
+          <t>Один блок «Как устроена ваша работа». Внутри две группы с нумерованными кружками: 1 «Сама съёмка» — минимальная длительность и кадры с часа; 2 «Работа вокруг съёмки» — обработка, общение, продвижение. Между группами воздух 30 px и тонкая черта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Образец для групп</t>
+        </is>
+      </c>
+      <c r="B248" s="229" t="inlineStr">
+        <is>
+          <t>.pgh и .pgd из блока 03 отчёта — те же кружок 30 px с градиентом, размер заголовка 17 px и подпись 13,5 px. Классы в анкете названы .grh, .grd, .grp — имена проверены, свободны. Второй кружок в синей гамме, чтобы группы различались.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Резерв на форс-мажоры</t>
+        </is>
+      </c>
+      <c r="B249" s="229" t="inlineStr">
+        <is>
+          <t>Был вопросом внутри блока 04, стал блоком 14 — оформлен как «Фонд развития»: рамка .zap с галочкой, ползунок 0-30 с заливкой дорожки и крупной цифрой. Гамма третьей рамки синяя: c-b-250 рамка, c-b-300 → c-b-600 дорожка, c-b-700 цифра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Что в скрипте</t>
+        </is>
+      </c>
+      <c r="B250" s="229" t="inlineStr">
+        <is>
+          <t>Отдельный обработчик $(fm_on).onchange убран — форс-мажор пошёл через общий зап(), тот же, что у фонда. Логика расчёта не тронута.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B251" s="229" t="inlineStr">
+        <is>
+          <t>Сверены 60 полей результата до и после: расхождений нет, ставка та же. Резерв влияет: при 20% ставка растёт с 9 874 до 12 342. Заливка дорожки: 0% пусто, 5% → 16,7%, 12% → 40%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>СТРАНИЦА ВХОДА ПЕРЕСОБРАНА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B253" s="229" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Полотно</t>
+        </is>
+      </c>
+      <c r="B254" s="229" t="inlineStr">
+        <is>
+          <t>Градиент лежит на всей странице, не на карточке: c-g-900 → c-g-800 → c-g-600 → c-g-500 по диагонали 150°. На html и body тот же тёмный тон, чтобы на длинном экране не было белых краёв. Шапки, строки со знаком и ссылки «Пропустить» больше нет — по краям пусто.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Знак</t>
+        </is>
+      </c>
+      <c r="B255" s="229" t="inlineStr">
+        <is>
+          <t>Крупный, по центру, столбиком: ромб 104 px, под ним слово 40 px и растянутая подпись «твоя юнит-экономика». Пропорции те же, что в шапке отчёта. Одна грань ромба светло-зелёная c-g-350, остальные белые — на тёмном фоне читается так же, как зелёная на светлом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Для кого</t>
+        </is>
+      </c>
+      <c r="B256" s="229" t="inlineStr">
+        <is>
+          <t>Ниже знака «Юнит-экономика для фотографа», вторая строка светло-зелёная. Под ней — «Создано фотографами для фотографов на основе реального опыта» и вторая фраза из шапки отчёта, слитые в один абзац.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Кнопка</t>
+        </is>
+      </c>
+      <c r="B257" s="229" t="inlineStr">
+        <is>
+          <t>«Просчитать юнит-экономику». Прозрачная, в белой рамке 2 px; при наведении заливается белым, надпись становится тёмно-зелёной. Высота 72 и радиус блока — как у кнопок отчёта. Под кнопкой строка «Бесплатно, без регистрации. Двадцать вопросов, пять минут».</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Шесть плашек</t>
+        </is>
+      </c>
+      <c r="B258" s="229" t="inlineStr">
+        <is>
+          <t>Стоимость часа · налоговый режим · скидки · неделя по часам · минимальная цена · цифры для прайса. Подложка светлее полотна: полупрозрачная белая заливка с двумя разными стопами и светлая грань. Значок в кружке, светло-зелёный. Три в ряд, на планшете два, на телефоне один.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Реквизиты</t>
+        </is>
+      </c>
+      <c r="B259" s="229" t="inlineStr">
+        <is>
+          <t>«ООО «Центр маркетинговых услуг Гет Маркетинг» © 2026» прижаты к низу экрана, приглушённые. Больше в подвале ничего нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Что осталось от прошлой версии</t>
+        </is>
+      </c>
+      <c r="B260" s="229" t="inlineStr">
+        <is>
+          <t>Перенос реферальной метки в анкету и память о визите phc_seen. Ссылки «Пропустить» больше нет — обход остался только через phc_seen и index.html?hello=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B261" s="229" t="inlineStr">
+        <is>
+          <t>Скобки, переменные, медиазапросы, дубли — чисто. Баланс тегов ноль. Метка ?ref=blog доходит до анкеты, phc_seen ставится по нажатию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>КНОПКА ВОЗВРАТА К ЗНАЧЕНИЯМ ПО УМОЛЧАНИЮ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B263" s="229" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Надпись</t>
+        </is>
+      </c>
+      <c r="B264" s="229" t="inlineStr">
+        <is>
+          <t>«Вернуть значения по умолчанию». Не «сбросить» и не «очистить»: поля не опустеют, а вернутся к нашим исходным цифрам — надпись должна обещать именно это.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="B265" s="229" t="inlineStr">
+        <is>
+          <t>Класс .btn.wh: белая, рамка 1,5 px, при наведении зелёная рамка и светло-зелёная подложка — форма от кнопок отчёта. Та же величина, что у зелёной: во всю колонку, высота 72, радиус блока. Стоит под ней, отступ 12 px. Фоновые ромбы зелёной кнопки в белой скрыты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="B266" s="229" t="inlineStr">
+        <is>
+          <t>Действие стирает всё введённое, поэтому спрашиваем — но не системным окном, а самой кнопкой: первое нажатие красит её в красный и меняет надпись на «Всё введённое будет стёрто — нажмите ещё раз», второе выполняет. Через пять секунд вопрос снимается сам. После возврата кнопка зеленеет с надписью «Значения возвращены» и через две секунды возвращается к обычному виду.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Что именно возвращается</t>
+        </is>
+      </c>
+      <c r="B267" s="229" t="inlineStr">
+        <is>
+          <t>Все поля и галочки — из снимка, снятого при загрузке уже после того, как таблицы расходов заполнены строками из CAT. Таблицы пересобираются заново: добавленные строки уходят, удалённые возвращаются. Восстанавливаются и состояния, которые ведёт скрипт: подсветка выбора, скрытые подблоки рабочего места, сайта и бухгалтерии, рамки запасов, ползунки и заливка их дорожек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Память</t>
+        </is>
+      </c>
+      <c r="B268" s="229" t="inlineStr">
+        <is>
+          <t>Стираются phc_state и phc_report — иначе отчёт открылся бы со старыми цифрами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B269" s="229" t="inlineStr">
+        <is>
+          <t>Испортили поля, галочки, режимы, добавили и удалили строки таблиц — после возврата состояние совпало с исходным посимвольно, число строк тоже. Расчёт после возврата сошёлся с первоначальным: 60 полей, ноль расхождений, ставка та же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ПЕРВЫЙ ЭКРАН ВХОДА — ЗНАК-КНОПКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B271" s="229" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Знак</t>
+        </is>
+      </c>
+      <c r="B272" s="229" t="inlineStr">
+        <is>
+          <t>Во весь первый экран: ромб от 150 до 300 px, слово «счетикс» до 104 px. Размеры вяжутся к высоте окна через clamp и vh, а не к ширине — иначе на ноутбуке знак не влезал бы в экран.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Подпись знака</t>
+        </is>
+      </c>
+      <c r="B273" s="229" t="inlineStr">
+        <is>
+          <t>Вместо «твоя юнит-экономика» — «юнит-экономика для фотографа», растянута ровно по ширине слова тем же приёмом, что в шапке отчёта. Отдельного заголовка «для фотографа» больше нет: он ушёл в подпись знака. Ключ bt_03 — в 09_Тексты не заведён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Вся рамка — одна кнопка</t>
+        </is>
+      </c>
+      <c r="B274" s="229" t="inlineStr">
+        <is>
+          <t>Первый экран это тег A с рамкой 2 px и радиусом 34. Внутри знак, строка «Создано фотографами…» и приглашение «Перейти к расчёту» со стрелкой. Нажатие в любом месте рамки ведёт в анкету. При наведении рамка светлеет, появляется подложка и тень, стрелка отъезжает вправо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Отдельной кнопки нет</t>
+        </is>
+      </c>
+      <c r="B275" s="229" t="inlineStr">
+        <is>
+          <t>Прежняя .cta убрана. Приглашение внутри рамки не кнопка, а надпись с подчёркиванием — иначе кнопка в кнопке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Плашки</t>
+        </is>
+      </c>
+      <c r="B276" s="229" t="inlineStr">
+        <is>
+          <t>Спущены под первый экран: рамка занимает высоту окна минус 150 px, поэтому плашки видно только после прокрутки — знаку дан воздух. Стали крупными и почти квадратными: минимум 230 px высоты, значок 58 px в кружке 16, заголовок 21 px. Три в ряд на десктопе, две на планшете, одна на телефоне. Плашки вне рамки — не кликаются, как вы и сказали.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B277" s="229" t="inlineStr">
+        <is>
+          <t>Скобки, переменные, медиазапросы, дубли — чисто. Вложенных ссылок внутри рамки нет. Метка ?ref=blog доходит до анкеты, phc_seen ставится по нажатию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ГЛАВНАЯ МЫСЛЬ НА СТРАНИЦЕ ВХОДА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B279" s="229" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B280" s="229" t="inlineStr">
+        <is>
+          <t>«Быть независимым автором не значит работать больше, чем в найме, и постоянно уходить в минус» вынесена отдельной строкой между первым экраном и плашками. Класс .creed, ключ wc_01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="B281" s="229" t="inlineStr">
+        <is>
+          <t>Крупный текст прямо по полотну: ни подложки, ни рамки, ни знака. Размер от 26 до 48 px, привязан к ширине окна. Ширина 1180 — как у плашек, но текст стоит один, поэтому читается шире их. По центру, полужирный, плотный межбуквенный.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Что изменилось рядом</t>
+        </is>
+      </c>
+      <c r="B282" s="229" t="inlineStr">
+        <is>
+          <t>Фраза была вторым предложением в абзаце .made внутри рамки. Там осталось только «Создано фотографами для фотографов на основе реального опыта» — без точки, это подпись, а не предложение. Отступ плашек теперь считается от фразы, а не от первого экрана.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Порядок на странице</t>
+        </is>
+      </c>
+      <c r="B283" s="229" t="inlineStr">
+        <is>
+          <t>Рамка-кнопка → главная мысль → шесть плашек → реквизиты. Фраза вне рамки, значит не кликается — нажимается только первый экран.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ПРАВКИ НА СТРАНИЦЕ ВХОДА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B285" s="229" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Пятое преимущество</t>
+        </is>
+      </c>
+      <c r="B286" s="229" t="inlineStr">
+        <is>
+          <t>«Минимальная цена часа» → «Точка безубыточности». Подпись переписана, иначе термин стоял бы дважды: «Цена часа, ниже которой вы работаете себе в убыток — спокойный ответ на просьбу о скидке».</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Подчёркивание убрано</t>
+        </is>
+      </c>
+      <c r="B287" s="229" t="inlineStr">
+        <is>
+          <t>У «Перейти к расчёту» снята нижняя рамка. Осталась стрелка: при наведении на первый экран она отъезжает вправо — этого хватает, чтобы понять, что экран нажимается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Строка убрана</t>
+        </is>
+      </c>
+      <c r="B288" s="229" t="inlineStr">
+        <is>
+          <t>«Бесплатно, без регистрации. Двадцать вопросов, пять минут» удалена вместе с правилом .undr. Ключ wu_01 больше не используется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Заголовок над плашками</t>
+        </is>
+      </c>
+      <c r="B289" s="229" t="inlineStr">
+        <is>
+          <t>«Что вы получите в отчёте», класс .advh, ключ wah_01. Тише главной мысли и крупнее плашек: 20–30 px, приглушённо-белый. Отступ плашек ужат, потому что теперь они идут от заголовка, а не от главной мысли.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Порядок на странице</t>
+        </is>
+      </c>
+      <c r="B290" s="229" t="inlineStr">
+        <is>
+          <t>Рамка-кнопка → главная мысль → заголовок → шесть плашек → реквизиты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ПОДВАЛ И РАЗМЕР ЗНАКА НА ВХОДЕ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B292" s="229" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Подвал</t>
+        </is>
+      </c>
+      <c r="B293" s="229" t="inlineStr">
+        <is>
+          <t>Был только строкой реквизитов. Стал таким же, как в анкете и отчёте: знак с растянутой подписью «твоя юнит-экономика», под ним ООО. Геометрия скопирована дословно — .lgs, .btx, .bd i, .lx совпадают с анкетой посимвольно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Отличие только в цвете</t>
+        </is>
+      </c>
+      <c r="B294" s="229" t="inlineStr">
+        <is>
+          <t>На тёмном полотне серый c-gr2 и c-gr3 не читаются. Слово белое с прозрачностью .82, подпись и реквизиты .45, грани ромба .62, одна грань светло-зелёная c-g-350 — как в самом знаке наверху.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Знак наверху крупнее</t>
+        </is>
+      </c>
+      <c r="B295" s="229" t="inlineStr">
+        <is>
+          <t>Ромб был 150–300 px, стал 170–370. Слово было 52–104 px, стало 58–126. Подпись 11–15 → 12–18. На телефоне ромб 140–200, слово 44–70.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Больше воздуха</t>
+        </is>
+      </c>
+      <c r="B296" s="229" t="inlineStr">
+        <is>
+          <t>Внутренние поля рамки были 28–64 px, стали 48–104 сверху и снизу и 32–72 по краям. Промежуток между знаком, строкой и приглашением 24–44 → 34–66. Между ромбом и словом 14–26 → 20–40. Сама рамка занимает высоту окна минус 120 px вместо 150 — за счёт этого знак дышит, а плашки по-прежнему уходят под сгиб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B297" s="229" t="inlineStr">
+        <is>
+          <t>Скобки, переменные, медиазапросы, дубли — чисто. Подвал вне кликабельной рамки: нажимается только первый экран.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ТОЧКИ ИЗ АНИМАЦИИ РАСЧЁТА УБРАНЫ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B299" s="229" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Что убрано</t>
+        </is>
+      </c>
+      <c r="B300" s="229" t="inlineStr">
+        <is>
+          <t>Второй слой .dots — шесть кружков по кругу с затухающей прозрачностью, вращались 5,5 с. Выглядели по-детски. Удалены разметка, правила .spin .dots и .spin .dots circle, кадры phcspin и правило prefers-reduced-motion, которое ими управляло — без точек ему нечего было выключать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Что осталось</t>
+        </is>
+      </c>
+      <c r="B301" s="229" t="inlineStr">
+        <is>
+          <t>Кольцо 200 px: серая дорожка и заливка градиентом c-g-350 → c-g-700, крупные проценты в центре, название этапа и подпись под ним. Ход кольца от 578 до нуля не тронут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B302" s="229" t="inlineStr">
+        <is>
+          <t>В кольце ровно два круга — фон и заливка. Ни одного следа dots и phcspin в файле. Расчёт идёт, проценты и этапы сменяются, кольцо доходит до конца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ШЕСТОЕ ПРЕИМУЩЕСТВО ЗАМЕНЕНО, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B304" s="229" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B305" s="229" t="inlineStr">
+        <is>
+          <t>«Готовые цифры для прайса» — это не польза для человека, а описание формата выдачи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B306" s="229" t="inlineStr">
+        <is>
+          <t>«Как распределяется ваше время» — заголовок блока 02 отчёта. Значок заменён на круговую диаграмму с выделенным сектором, вместо прежнего листа с таблицей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Развели с четвёртой плашкой</t>
+        </is>
+      </c>
+      <c r="B307" s="229" t="inlineStr">
+        <is>
+          <t>Четвёртая «Ваша неделя по часам» — про сетку пяти дней и остаётся ли время на жизнь. Шестая — про раскладку по видам работ: «Сколько часов уходит на съёмку, обработку, переговоры и продвижение — и за что вам платят на самом деле». Темы соседние, поэтому подписи разведены явно: одна про календарь, другая про роли.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B308" s="229" t="inlineStr">
+        <is>
+          <t>Шесть плашек, тексты на местах, баланс тегов ноль, проверка вёрстки чистая.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ЧЕТВЁРТОЕ ПРЕИМУЩЕСТВО ЗАМЕНЕНО, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B310" s="229" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B311" s="229" t="inlineStr">
+        <is>
+          <t>«Ваша неделя по часам» — сетка пяти дней. Пересекалась с шестой плашкой про распределение времени.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B312" s="229" t="inlineStr">
+        <is>
+          <t>«Куда уходит каждый рубль клиента» — главная диаграмма отчёта, блок 01. Подпись: «Подробная разбивка часа: сколько заберут техника, реклама, аренда и налоги, а сколько останется вам».</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Итоговый набор</t>
+        </is>
+      </c>
+      <c r="B313" s="229" t="inlineStr">
+        <is>
+          <t>Стоимость часа · налоговый режим · скидки · разбивка рубля · точка безубыточности · распределение времени. Дублей нет: четвёртая про деньги, шестая про часы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Значки развели</t>
+        </is>
+      </c>
+      <c r="B314" s="229" t="inlineStr">
+        <is>
+          <t>Четвёртая получила кольцо с секторами разной насыщенности — как диаграмма блока 01. Шестая была тоже круговой диаграммой, стала циферблатом со стрелками: рядом стоящие плашки не должны выглядеть одинаково.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B315" s="229" t="inlineStr">
+        <is>
+          <t>Шесть плашек, тексты на местах, баланс тегов ноль, проверка вёрстки чистая.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ВЕРХНИЙ ФОНОВЫЙ РИСУНОК НА ВХОДЕ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B317" s="229" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B318" s="229" t="inlineStr">
+        <is>
+          <t>Верхний левый ромб .d1 заменён на фотоаппарат. Контур взят у .h2i — фонового значка в шапке отчёта, добавлена точка видоискателя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Почему другие размеры</t>
+        </is>
+      </c>
+      <c r="B319" s="229" t="inlineStr">
+        <is>
+          <t>Ромб — сплошная заливка, фотоаппарат рисуется обводкой. Тонкие линии на градиенте почти пропадают, поэтому рисунок крупнее (520 против 440) и заметнее (прозрачность .085 против .05), а обводка утоньшена до 0,55 — при таком размере линия отчёта смотрелась бы жирной.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Что не тронуто</t>
+        </is>
+      </c>
+      <c r="B320" s="229" t="inlineStr">
+        <is>
+          <t>Нижний правый ромб .d2 остался как был. Слой .deco по-прежнему не перехватывает нажатия и скрыт от чтения с экрана.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ПОДСКАЗКИ НА ЛЕПЕСТКАХ ЗНАКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B322" s="229" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Фотоаппарат убран</t>
+        </is>
+      </c>
+      <c r="B323" s="229" t="inlineStr">
+        <is>
+          <t>Верхний фоновый рисунок вернулся к ромбу-заливке, как был. Размер и прозрачность прежние.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Четыре лепестка</t>
+        </is>
+      </c>
+      <c r="B324" s="229" t="inlineStr">
+        <is>
+          <t>Знак на входе разобран на четыре части юнит-экономики, по часовой стрелке от верхнего: Доход · Время · Расходы · Налоги. Подписи: что вы хотите получать на руки; съёмка, обработка, переговоры и продвижение; техника, аренда, реклама, подписки и учёба; ставка режима, взносы и комиссия банка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Цвета</t>
+        </is>
+      </c>
+      <c r="B325" s="229" t="inlineStr">
+        <is>
+          <t>Взяты из диаграммы блока 01 отчёта: доход c-a-400, время c-g-500, расходы c-v-500, налоги c-b-500. По умолчанию знак выглядит как везде — три белые грани и одна светло-зелёная; зелёный лепесток при наведении просто становится насыщеннее, с c-g-350 до c-g-500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Поведение</t>
+        </is>
+      </c>
+      <c r="B326" s="229" t="inlineStr">
+        <is>
+          <t>Наведённый лепесток заливается своим цветом и чуть увеличивается, остальные притухают до .42 — иначе непонятно, к чему относится подсказка. На устройствах без мыши подсказки и увеличение отключены медиазапросом hover:none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Подсказка</t>
+        </is>
+      </c>
+      <c r="B327" s="229" t="inlineStr">
+        <is>
+          <t>Образец — .segtip из отчёта: белая плашка, светлая рамка, тот же радиус и тень. Цветная метка слева повторяет цвет лепестка через переменную --tipc. Появляется под знаком по центру.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Доступность</t>
+        </is>
+      </c>
+      <c r="B328" s="229" t="inlineStr">
+        <is>
+          <t>У знака теперь role=img и aria-label «Счетикс» вместо aria-hidden: он перестал быть чисто декоративным, раз с ним взаимодействуют.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B329" s="229" t="inlineStr">
+        <is>
+          <t>Все четыре подсказки открываются и закрываются, цвет метки совпадает с цветом лепестка. Скобки, переменные, медиазапросы, дубли — чисто.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ПОДСКАЗКА С ЛЕПЕСТКОВ УБРАНА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B331" s="229" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+      <c r="B332" s="229" t="inlineStr">
+        <is>
+          <t>Знак на входе занимает почти весь экран: снизу к нему вплотную примыкает слово «счетикс», сверху плашка вылезала за край окна. Ставить её было некуда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Что удалено</t>
+        </is>
+      </c>
+      <c r="B333" s="229" t="inlineStr">
+        <is>
+          <t>Плашка .pettip, обёртка .bxw, все её правила, медиазапрос hover:none и массив ЛЕПЕСТКИ с текстами в скрипте. Следов не осталось.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Что оставлено</t>
+        </is>
+      </c>
+      <c r="B334" s="229" t="inlineStr">
+        <is>
+          <t>Подсветка при наведении: лепесток заливается своим цветом — доход c-a-400, время c-g-500, расходы c-v-500, налоги c-b-500 — остальные притухают до .4. Классы hot и dim по-прежнему вешает скрипт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ОШИБКА: знак развалился, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B335" s="229" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Что произошло</t>
+        </is>
+      </c>
+      <c r="B336" s="229" t="inlineStr">
+        <is>
+          <t>При первой версии подсказок лепесткам добавили transform:scale и transform-box:fill-box. Поворот ромбов задан атрибутом rotate(45 …) прямо в разметке — CSS-transform перебил его точку отсчёта, и знак рассыпался.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Правило</t>
+        </is>
+      </c>
+      <c r="B337" s="229" t="inlineStr">
+        <is>
+          <t>НЕ трогать transform у элементов знака. Отклик на наведение давать только цветом и прозрачностью. В файле оставлено предупреждение прямо над правилами .pet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Как проверять</t>
+        </is>
+      </c>
+      <c r="B338" s="229" t="inlineStr">
+        <is>
+          <t>jsdom не считает геометрию — рассыпавшийся знак он показывает исправным. Нужен настоящий браузер: puppeteer, снимок области знака и сверка координат четырёх лепестков на симметрию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ПРОБНЫЙ РЕЖИМ — ПОМЕТКИ ВО ВСЕХ ФАЙЛАХ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B340" s="229" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>index — строка сверху</t>
+        </is>
+      </c>
+      <c r="B341" s="229" t="inlineStr">
+        <is>
+          <t>Над рамкой-кнопкой, по центру: кружок с восклицательным знаком и «Пробный режим. Проверяем расчёт на реальных задачах». Полупрозрачная подложка, скруглённая — приглушена, чтобы не спорить со знаком. Ключ wt_01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>index — блок внизу</t>
+        </is>
+      </c>
+      <c r="B342" s="229" t="inlineStr">
+        <is>
+          <t>Под шестью плашками: «Что значит пробный режим», три абзаца. Подложка как у плашек, но во всю ширину — это сноска ко всей странице, а не седьмое преимущество. Ключи wt_02 … wt_05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>calc — меню</t>
+        </is>
+      </c>
+      <c r="B343" s="229" t="inlineStr">
+        <is>
+          <t>Слева в строке со знаком: пометка о пробном режиме и две кнопки — «Поделиться» и «Поблагодарить проект». Кнопки и подсказки перенесены из отчёта дословно, вместе с гаммой c-ig-1…4, которой в анкете не было. Прижим знака вправо снят: теперь слева есть содержимое. На узком экране пометка сжимается, на телефоне скрывается. Ключ ct_01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>calc — блок внизу</t>
+        </is>
+      </c>
+      <c r="B344" s="229" t="inlineStr">
+        <is>
+          <t>Под кнопками «Рассчитать» и «Вернуть значения», перед подвалом. Текст тот же, что на входе, оформление в песочной гамме карточки. При печати скрыт. Ключи ct_02 … ct_05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>report — только значок</t>
+        </is>
+      </c>
+      <c r="B345" s="229" t="inlineStr">
+        <is>
+          <t>Объяснения нет, как и договаривались. В оба меню — верхнее и плавающее — добавлен значок: восклицательный знак в треугольнике, подсказка «Калькулятор работает в пробном режиме». Форма .fbi общая с остальными значками, цвет янтарный c-a-500. Не кнопка: cursor:default, нажимать нечего.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Работа кнопок в анкете</t>
+        </is>
+      </c>
+      <c r="B346" s="229" t="inlineStr">
+        <is>
+          <t>«Поделиться» — тот же приём, что в отчёте: на телефонах системное окно, иначе копия ссылки в буфер и отметка на кнопке. Адрес благодарности берётся из THANKS_URL, пока заглушка #thanks — как в отчёте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B347" s="229" t="inlineStr">
+        <is>
+          <t>Все четыре места сняты и просмотрены: строка и блок на входе, меню и блок в анкете, треугольник в ряду значков отчёта. Сверка сборки показала только новые правила .fbt, чужое не задето.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>РАЗДЕЛ РЕЗЕРВОВ И ЕДИНАЯ ПОДСВЕТКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B349" s="229" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Заголовок раздела</t>
+        </is>
+      </c>
+      <c r="B350" s="229" t="inlineStr">
+        <is>
+          <t>Перед блоком 14 добавлен разделитель .sect «Теперь заложите резервы» с подзаголовком: расходы выше — то, без чего работа не состоится, резервы — запас на случившееся и на то, что хотите себе позволить; не заложите в цену — заплатите из дохода. Оформление то же, что у раздела «Как мы считаем». Ключи h2_rez и ss_rez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Значения по умолчанию</t>
+        </is>
+      </c>
+      <c r="B351" s="229" t="inlineStr">
+        <is>
+          <t>Форс-мажоры 10%, фонд развития 15%, запас на скидку 15% — ступень «полная программа». Раньше стояли 5, 5 и 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Единый сценарий цвета</t>
+        </is>
+      </c>
+      <c r="B352" s="229" t="inlineStr">
+        <is>
+          <t>Цвет зависит от значения, а не от того, какой это резерв. Ноль — красный, ниже рекомендованного — жёлтый, рекомендованное и выше — зелёный. У запаса на скидку: 15% зелёный, 10% синий, 5% жёлтый. Классы st-bad, st-warn, st-mid, st-ok вешает скрипт на рамку .zap, дальше цвет разбирает CSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Что красится</t>
+        </is>
+      </c>
+      <c r="B353" s="229" t="inlineStr">
+        <is>
+          <t>Рамка и подложка блока, заливка дорожки (--zc1 и --zc2, оба стопа разные), обводка бегунка и крупная цифра. Плюс строка под ползунком с объяснением, почему такой цвет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Галочка</t>
+        </is>
+      </c>
+      <c r="B354" s="229" t="inlineStr">
+        <is>
+          <t>Всегда зелёная, при любом значении: она про «учитывать резерв», а не про то, хватает ли его.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Выключенный резерв</t>
+        </is>
+      </c>
+      <c r="B355" s="229" t="inlineStr">
+        <is>
+          <t>Ползунок стоит на рекомендованном значении, цифра его показывает, но оба приглушены — видно, что это рекомендация, а не то, что идёт в расчёт. Раньше показывался ноль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Убрано</t>
+        </is>
+      </c>
+      <c r="B356" s="229" t="inlineStr">
+        <is>
+          <t>Классы .zap.b и .zap.c вместе с их правилами: цвет больше не привязан к блоку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО: дубль номера</t>
+        </is>
+      </c>
+      <c r="B357" s="229" t="inlineStr">
+        <is>
+          <t>Раздел «Как мы считаем» носил кружок 03 — тот же номер, что у карточки «Ваша текущая ставка». Номер у раздела снят: нумеруются только карточки с вопросами. Теперь 01…16 без повторов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B358" s="229" t="inlineStr">
+        <is>
+          <t>Сняты и просмотрены все состояния: выключено, 10% зелёное, 3% жёлтое, 0% красное. Ступени скидки: 15 зелёная, 10 синяя, 5 жёлтая. Расчёт при снятых галочках не изменился — 60 полей, ноль расхождений, ставка та же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ПРОБНЫЙ РЕЖИМ — ПРИВЕДЕНО К ОДНОМУ ВИДУ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B360" s="229" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Единый значок</t>
+        </is>
+      </c>
+      <c r="B361" s="229" t="inlineStr">
+        <is>
+          <t>Треугольник с восклицательным знаком из меню отчёта. Класс .tri, размер 17 px в пометках и 21–22 px в заголовках блоков. Шесть штук: по два в index, calc и report. Прежние кружки с «!» убраны — они были разные в каждом месте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Единые слова</t>
+        </is>
+      </c>
+      <c r="B362" s="229" t="inlineStr">
+        <is>
+          <t>На входе «Сервис работает в пробном режиме», в подсказке отчёта то же самое. В анкете короче — «Пробный режим». Заголовок блока везде «Что значит пробный режим». Слово «калькулятор» из подсказки убрано: сервис, а не калькулятор.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Подложек нет</t>
+        </is>
+      </c>
+      <c r="B363" s="229" t="inlineStr">
+        <is>
+          <t>Пометка на входе и в меню анкеты — просто текст со значком, без плашки и рамки. Блок с объяснением на входе тоже без подложки, в анкете отделён сверху тонкой чертой, как обёртка кнопок. Раньше и то и другое было в жёлтой плашке — читалось как предупреждение об ошибке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Текст переписан</t>
+        </is>
+      </c>
+      <c r="B364" s="229" t="inlineStr">
+        <is>
+          <t>Три абзаца: сервис уже работает и считает по открытой методике; мы всё ещё тестируем, может встретиться ошибка — напишите, будем благодарны; оплата отчёта тоже пока в пробном режиме, сейчас это скорее способ поддержать проект, чем цена. Про будущую платность прямо не сказано — читается из контекста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Подсказка только в основном меню</t>
+        </is>
+      </c>
+      <c r="B365" s="229" t="inlineStr">
+        <is>
+          <t>В плавающей плашке отчёта у значка снят data-tip: там подсказка перекрывала бы содержимое. В верхнем меню осталась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО: дубль</t>
+        </is>
+      </c>
+      <c r="B366" s="229" t="inlineStr">
+        <is>
+          <t>#phc-root .zap:not(.on) .zaprow output задано дважды — остаток правки резервов. Второе правило, без opacity, убрано.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B367" s="229" t="inlineStr">
+        <is>
+          <t>Сняты и просмотрены все четыре места. Значки одинаковые, старых кружков нет, подсказка в плавающем меню отсутствует. Сверка сборки отчёта: изменений в оформлении нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ЗОНИРОВАНИЕ АНКЕТЫ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B369" s="229" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Три раздела</t>
+        </is>
+      </c>
+      <c r="B370" s="229" t="inlineStr">
+        <is>
+          <t>Анкета разбита разделителями .sect: «Как мы считаем» (было), «Теперь посчитаем расходы» (новый, перед блоком 05) и «Теперь заложите резервы» (перед блоком 14). Ключи h2_rash и ss_rash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Текст раздела расходов</t>
+        </is>
+      </c>
+      <c r="B371" s="229" t="inlineStr">
+        <is>
+          <t>Всё, на что уже потратились или тратитесь регулярно. Чем точнее внесёте, тем ближе к правде ставка — считаем от ваших цифр, а не от средних по рынку. Если собирать чеки некогда, оставьте наш набор: он по реальным ценам и даст приблизительный, но осмысленный результат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Блок 04 переименован</t>
+        </is>
+      </c>
+      <c r="B372" s="229" t="inlineStr">
+        <is>
+          <t>«Как устроена ваша работа» → «Посчитаем ваше время». Подзаголовок поправлен под новый заголовок. Ключ h2_04 в книге обновлён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>УВЕДОМЛЕНИЯ О ЛИМИТЕ ПЕРЕПИСАНЫ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B373" s="229" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Плашка в форме</t>
+        </is>
+      </c>
+      <c r="B374" s="229" t="inlineStr">
+        <is>
+          <t>Под выбором режима. Раньше показывала выручку, процент от лимита и остаток до порога. Теперь это форма, а не результат: цифр нет вовсе. Одно состояние — модель не помещается в режим, мягкий жёлтый. Красное состояние .lim.over удалено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Текст плашки</t>
+        </is>
+      </c>
+      <c r="B375" s="229" t="inlineStr">
+        <is>
+          <t>Для НПД: «Ваша финансовая модель больше не подходит под самозанятость: доход выше нормы, установленной законом. С такими цифрами работать можно только как ИП». Для остальных режимов — то же, но с предложением выбрать режим без ограничения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Полоса внизу</t>
+        </is>
+      </c>
+      <c r="B376" s="229" t="inlineStr">
+        <is>
+          <t>Нужна ровно для одного: сказать, что режим переключился на ИП. Показывается только при ПЕРЕКЛЮЧЕНО. Убраны состояния warn/over/ok, колонки «Ваша выручка» и «Запас до лимита», пороги 80% и 100 000 ₽, сообщения «Готово» и «Отлично». Фон белый, знак — тот же треугольник, что во всех пометках о пробном режиме.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Когда исчезает</t>
+        </is>
+      </c>
+      <c r="B377" s="229" t="inlineStr">
+        <is>
+          <t>Как только человек поправит цифры и снова влезет в лимит НПД, ПЕРЕКЛЮЧЕНО снимается и полоса уходит сама. Отдельного сообщения «всё в порядке» больше нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Убрано из скрипта</t>
+        </is>
+      </c>
+      <c r="B378" s="229" t="inlineStr">
+        <is>
+          <t>Переменные ВЕРНУЛОСЬ и БЫЛО_ПРЕВЫШЕНИЕ — они обслуживали удалённые сообщения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B379" s="229" t="inlineStr">
+        <is>
+          <t>Доход задран → режим переключился, плашка в форме молчит, при прокрутке вниз появляется белая полоса. Доход вернули → полоса исчезла. Доход выше УСН → жёлтая плашка без цифр. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>БЛОК 03 «ВАША ТЕКУЩАЯ СТАВКА», 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B381" s="229" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B382" s="229" t="inlineStr">
+        <is>
+          <t>Приведён к виду блока 01 «Ваш доход»: вопрос .qr wide во всю ширину, поле под ним отдельной строкой шириной 340. Из подсказки убрано «Нужно, чтобы показать разницу между вашей текущей и расчётной ставкой» — это уже сказано в подзаголовке блока. Осталось «Можно указать примерно».</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>РАБОТА БЕЗ ОФОРМЛЕНИЯ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B383" s="229" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Галочка</t>
+        </is>
+      </c>
+      <c r="B384" s="229" t="inlineStr">
+        <is>
+          <t>В блоке 02 добавлена «Работаю без оформления — налоги не считать». Форма .exc — та же, что у «не учитывать этот блок», и такая же красная. Под ней пояснение: доход без оформления это работа вне закона, штрафы и доначисления считаются за три года, подтвердить доход для ипотеки или визы будет нечем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Что происходит</t>
+        </is>
+      </c>
+      <c r="B385" s="229" t="inlineStr">
+        <is>
+          <t>Список режимов и вопрос о заказчиках гаснут и блокируются, плашка о лимите не показывается. В расчёте ставка режима обнуляется, taxOf возвращает ноль, фиксированные взносы не прибавляются. Проверено: taxAll = 0, ставка падает с 9 874 до 9 367.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ВОПРОС О ЗАКАЗЧИКАХ — ТОЛЬКО НА НПД, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B386" s="229" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+      <c r="B387" s="229" t="inlineStr">
+        <is>
+          <t>На НПД ставка прямо зависит от заказчика: 4% с частных лиц, 6% с компаний. На УСН и АУСН ставка одна для всех — вопрос только путал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Что было</t>
+        </is>
+      </c>
+      <c r="B388" s="229" t="inlineStr">
+        <is>
+          <t>Два противоречащих комментария подряд: один говорил «только на НПД», второй «при любом режиме». Работал второй — вопрос висел всегда. Оставлен один, добавлена функция ктоВидим().</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ПРОБНЫЙ РЕЖИМ: ССЫЛКИ И БЛОК В ОТЧЁТЕ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B389" s="229" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Подсказка в анкете</t>
+        </is>
+      </c>
+      <c r="B390" s="229" t="inlineStr">
+        <is>
+          <t>Пометка в меню стала ссылкой на #trial. При наведении всплывает «Сервис работает в пробном режиме» — оформление то же, что у значков меню отчёта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Переход к объяснению</t>
+        </is>
+      </c>
+      <c r="B391" s="229" t="inlineStr">
+        <is>
+          <t>Все пометки ведут на блок #trial внизу своей страницы. При переходе блок подсвечивается на 2,4 секунды через :target — иначе непонятно, куда попал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Блок в отчёте</t>
+        </is>
+      </c>
+      <c r="B392" s="229" t="inlineStr">
+        <is>
+          <t>Добавлен перед подвалом, дословная копия того, что в анкете. Человека больше не перекидывает из отчёта в калькулятор — данные не сбиваются. Ключи rt_01 … rt_04. Значок в верхнем меню стал ссылкой, в плавающей плашке остался span без подсказки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Кнопка на входе</t>
+        </is>
+      </c>
+      <c r="B393" s="229" t="inlineStr">
+        <is>
+          <t>Под объяснением «Перейти к расчёту», форма от кнопок отчёта. Человек дочитал — дальше ему нужен путь к расчёту, а не возврат наверх. Реферальную метку и память о визите несёт наравне с главной.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>собрать.py</t>
+        </is>
+      </c>
+      <c r="B394" s="229" t="inlineStr">
+        <is>
+          <t>ожидать_блоков: 23 → 24. Проверка структуры сама поймала новый блок и остановила сборку — это правильно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>САМОЗАНЯТОСТЬ УБИРАЕТСЯ ИЗ СПИСКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B396" s="229" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+      <c r="B397" s="229" t="inlineStr">
+        <is>
+          <t>Оставлять НПД в списке, когда доход выше лимита, — значит предлагать заведомо невозможный вариант: человек выберет, и расчёт снова выкинет его на ИП. Пункт скрывается и блокируется, пока нужный доход выше 2 400 000 ₽. Вернутся цифры в лимит — пункт вернётся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Текст полосы</t>
+        </is>
+      </c>
+      <c r="B398" s="229" t="inlineStr">
+        <is>
+          <t>Было одной строкой с обещанием «режим можно сменить вручную» — неправда, сменить на НПД уже нельзя. Стало: заголовок «Налоговый режим переключён на ИП» отдельной строкой, ниже объяснение: доход, который вам нужен, выше нормы для самозанятых, поэтому самозанятость больше недоступна и убрана из списка; между режимами ИП выбирать можно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО: вопрос о заказчиках</t>
+        </is>
+      </c>
+      <c r="B399" s="229" t="inlineStr">
+        <is>
+          <t>При автоматической смене режима вопрос «С кем вы чаще работаете» оставался на экране — обработчик change при программной смене не срабатывает. Добавлен прямой вызов ктоВидим().</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО: дубль .lbt</t>
+        </is>
+      </c>
+      <c r="B400" s="229" t="inlineStr">
+        <is>
+          <t>#phc-root .limbar .lbt было задано дважды — остаток моей прошлой правки. Слито в одно правило.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B401" s="229" t="inlineStr">
+        <is>
+          <t>Доход задран → НПД скрыт, пунктов 4, вопрос о заказчиках ушёл, полоса с двумя строками. Доход вернули → НПД снова в списке, пунктов 5, полоса исчезла. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>БЛОК 03: ВОПРОС УБРАН, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B403" s="229" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Что удалено</t>
+        </is>
+      </c>
+      <c r="B404" s="229" t="inlineStr">
+        <is>
+          <t>Строки «Сколько вы берёте за час съёмки сейчас?» и «Можно указать примерно» — они повторяли заголовок и подзаголовок блока. Ключи q_03 и qd_03 помечены красным в 09_Тексты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Что осталось</t>
+        </is>
+      </c>
+      <c r="B405" s="229" t="inlineStr">
+        <is>
+          <t>Заголовок «Ваша текущая ставка», подзаголовок «С ней мы сравним расчётную — чтобы вы увидели разницу в год и в месяц» и поле. Поле current_rate не тронуто, расчёт сошёлся: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ГАЛОЧКА В БЛОКЕ НАЛОГОВ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B407" s="229" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Метка</t>
+        </is>
+      </c>
+      <c r="B408" s="229" t="inlineStr">
+        <is>
+          <t>«Работаю без оформления — налоги не считать» → «Не учитывать этот блок в расчёте». Такая же, как во всех блоках расходов: единый приём, отдельная формулировка не нужна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Текст пояснения</t>
+        </is>
+      </c>
+      <c r="B409" s="229" t="inlineStr">
+        <is>
+          <t>Убрано «Тогда налоги и взносы в расчёт не войдут» — это и так очевидно из метки. Убрано про ипотеку и визы. Написано: рекомендуем выбрать подходящий режим; работая без оформления, вы делаете цену ниже за свой счёт — по сути платите налог из своего кармана, чтобы заказчику было дешевле; закладывать налог в цену нормально, так делают все; при проверке налоговая может доначислить за три года.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Тон</t>
+        </is>
+      </c>
+      <c r="B410" s="229" t="inlineStr">
+        <is>
+          <t>Плашка была красной, стала нейтральной: серый текст на светлой подложке. Это совет, а не предупреждение о наказании — пугать проверками не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B411" s="229" t="inlineStr">
+        <is>
+          <t>Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>БЛОК ВРЕМЕНИ РАЗБИТ НА КАРТОЧКИ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B413" s="229" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B414" s="229" t="inlineStr">
+        <is>
+          <t>Одна карточка «Посчитаем ваше время» с двумя группами внутри — «Сама съёмка» и «Работа вокруг съёмки», с нумерованными кружками и своими подписями. Читалось тяжело.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B415" s="229" t="inlineStr">
+        <is>
+          <t>Раздел .sect «Структурируем ваше время» с подзаголовком в две строки, под ним пять отдельных карточек: Минимальная съёмка · Кадры с одной съёмки · Обработка материала · Общение с клиентом · Продвижение. В каждой только заголовок, подзаголовок и поле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Подзаголовки</t>
+        </is>
+      </c>
+      <c r="B416" s="229" t="inlineStr">
+        <is>
+          <t>Взяты готовые тексты .qd из книги — они точнее выдуманных заново. Свои варианты, написанные при первой сборке, убраны: две строки об одном под каждым заголовком не нужны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Что сохранено</t>
+        </is>
+      </c>
+      <c r="B417" s="229" t="inlineStr">
+        <is>
+          <t>Раскрывашки «что сюда входит» в трёх карточках — на них ссылается справочник отчёта. Все поля и их id не тронуты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Убрано</t>
+        </is>
+      </c>
+      <c r="B418" s="229" t="inlineStr">
+        <is>
+          <t>Классы .grp, .grh, .grd и их правила — групп внутри карточек больше нет. Ключи h2_04, hint_01, q_04, q_04b, q_05, q_06, q_07, grd_01, grd_02 помечены красным в 09_Тексты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Раздел расходов</t>
+        </is>
+      </c>
+      <c r="B419" s="229" t="inlineStr">
+        <is>
+          <t>«Теперь посчитаем расходы» → «Учтём все расходы». Подзаголовок сокращён до двух строк: всё, на что уже потратились или тратитесь регулярно; чем точнее внесёте, тем ближе к правде ставка — можете воспользоваться значениями по умолчанию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Нумерация</t>
+        </is>
+      </c>
+      <c r="B420" s="229" t="inlineStr">
+        <is>
+          <t>Карточек стало 20 вместо 16. Разделы .sect номеров не носят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B421" s="229" t="inlineStr">
+        <is>
+          <t>Расчёт не изменился: 60 полей, ноль расхождений, ставка та же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>«ВЕРНУТЬ ЗНАЧЕНИЕ» ПОД КАЖДЫМ ПОЛЕМ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B423" s="229" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B424" s="229" t="inlineStr">
+        <is>
+          <t>Под каждым числовым полем — тихая строчка «Вернуть значение по умолчанию». 21 поле. Появляется, только когда цифра отличается от исходной: пока человек ничего не менял, её нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Как устроено</t>
+        </is>
+      </c>
+      <c r="B425" s="229" t="inlineStr">
+        <is>
+          <t>Строчки создаёт скрипт при загрузке, обходя все .qf input[type=number] с id. Исходное берём из атрибута value в разметке — там же, откуда его берёт браузер, второго источника правды не заводим. Будущие поля подхватятся сами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Чего не касается</t>
+        </is>
+      </c>
+      <c r="B426" s="229" t="inlineStr">
+        <is>
+          <t>Таблиц расходов: там строки добавляются и удаляются, «исходного значения» у них нет. Для них работает общая кнопка «Вернуть значения по умолчанию» внизу анкеты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>АВТОПОДБОР НАЛОГОВОГО РЕЖИМА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B427" s="229" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Галочка</t>
+        </is>
+      </c>
+      <c r="B428" s="229" t="inlineStr">
+        <is>
+          <t>«Подобрать режим автоматически», стоит по умолчанию. Под ней правило: из доступных режимов берём тот, где на руки остаётся больше; учитываем ставку, взносы и лимиты. Снял галочку — выбирай сам, список разблокируется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Как считает</t>
+        </is>
+      </c>
+      <c r="B429" s="229" t="inlineStr">
+        <is>
+          <t>Функция подобрать() перебирает npd, usn6, usn15, ausn8, ausn20, считает каждый и сравнивает выручку минус расходы, налоги и эквайринг. Режимы, в лимит которых человек не помещается, отбрасываются. Правило то же, что в блоке «Ваш идеальный налоговый режим» отчёта — иначе анкета и отчёт советовали бы разное.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Список</t>
+        </is>
+      </c>
+      <c r="B430" s="229" t="inlineStr">
+        <is>
+          <t>Пока подбор включён, список показывает выбранный режим, но не даёт менять: иначе человек выберет, а расчёт тут же переставит обратно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>ТЕКСТ УВЕДОМЛЕНИЯ О ПЕРЕКЛЮЧЕНИИ</t>
+        </is>
+      </c>
+      <c r="B431" s="229" t="inlineStr">
+        <is>
+          <t>Убрано «из списка она убрана» и «между режимами ИП выбирать можно» — это описание нашей механики, а не ответ на вопрос «что мне делать». Написано: чтобы вернуться на самозанятость, нужно уменьшить желаемый доход в первом блоке; советуем сначала заполнить анкету до конца — когда будут учтены все расходы, станет ясно, насколько его надо менять.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B432" s="229" t="inlineStr">
+        <is>
+          <t>Расчёт по умолчанию не изменился: 60 полей, ноль расхождений. Строчка возврата появляется по изменению и возвращает цифру. Автоподбор при доходе 250 000 переставил НПД на УСН 6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ПРАВКИ ПО НАЛОГОВОМУ БЛОКУ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B434" s="229" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Полоса видна везде</t>
+        </is>
+      </c>
+      <c r="B435" s="229" t="inlineStr">
+        <is>
+          <t>Убрано условие, прятавшее полосу, когда блок налогов на экране. Смена режима — то, что человек должен заметить сразу, где бы он ни был. Раньше при правке дохода наверху страницы уведомление не показывалось вовсе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Автоподбор выключен по умолчанию</t>
+        </is>
+      </c>
+      <c r="B436" s="229" t="inlineStr">
+        <is>
+          <t>Галочка «Подобрать режим автоматически» больше не стоит при открытии: человек сам решает, доверить выбор калькулятору или выбрать режим.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Блокировка полная</t>
+        </is>
+      </c>
+      <c r="B437" s="229" t="inlineStr">
+        <is>
+          <t>При включённом автоподборе блокируется не только список режимов, но и вопрос «С кем вы чаще работаете» — от него зависит ставка НПД, значит он тоже часть выбора. Обе галочки, автоподбор и «не учитывать блок», согласованы: каждая проверяет состояние другой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B438" s="229" t="inlineStr">
+        <is>
+          <t>Доход задран без прокрутки — полоса появилась сразу. Автоподбор включён — оба поля заблокированы, режим подобран. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ТЕКСТ ПОДТВЕРЖДЕНИЯ СБРОСА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B440" s="229" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B441" s="229" t="inlineStr">
+        <is>
+          <t>«Всё введённое будет стёрто — нажмите ещё раз». Слово «стёрто» пугало и было неточным: поля не опустеют, а вернутся к исходным цифрам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B442" s="229" t="inlineStr">
+        <is>
+          <t>«Все введённые данные будут изменены. Нажмите ещё раз, чтобы подтвердить».</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>На заметку</t>
+        </is>
+      </c>
+      <c r="B443" s="229" t="inlineStr">
+        <is>
+          <t>В строках JS кириллица записана через \uXXXX, причём регистр букв в escape-последовательностях смешанный: \u043D рядом с \u0435. Поиск по подготовленной строке не сработает — заменять надо по позиции в файле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>АВТОПОДБОР ВЫДЕЛЕН РАМКОЙ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B445" s="229" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Образец</t>
+        </is>
+      </c>
+      <c r="B446" s="229" t="inlineStr">
+        <is>
+          <t>Рамка .zap из блоков резервов: то же скругление 14, та же подложка c-surf, тот же переход цвета. Новый класс .autobox — имя проверено, свободно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Как ведёт себя</t>
+        </is>
+      </c>
+      <c r="B447" s="229" t="inlineStr">
+        <is>
+          <t>Пока галочка снята, рамка серая и пояснение скрыто. Поставили — рамка и подложка зеленеют, значок из серого становится зелёным, пояснение раскрывается. Это же поведение у рамок резервов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Надпись</t>
+        </is>
+      </c>
+      <c r="B448" s="229" t="inlineStr">
+        <is>
+          <t>Стала крупнее и полужирной, как заголовки .zaph .flag. Между галочкой и надписью — значок-искра, он подхватывает цвет состояния.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B449" s="229" t="inlineStr">
+        <is>
+          <t>Рамка зеленеет, оба поля блокируются, режим подбирается. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>АВТОПОДБОР СТАЛ КНОПКОЙ-ПЕРЕКЛЮЧАТЕЛЕМ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B451" s="229" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Что сделано</t>
+        </is>
+      </c>
+      <c r="B452" s="229" t="inlineStr">
+        <is>
+          <t>Вместо рамки с галочкой — кнопка .autobtn во всю ширину, надпись по центру. Нажатие переключает: первое включает подбор, второе выключает. Настоящий флажок лежит внутри и скрыт, состояние читается через :has(input:checked) — отдельного класса и его переключения в скрипте больше нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Два состояния</t>
+        </is>
+      </c>
+      <c r="B453" s="229" t="inlineStr">
+        <is>
+          <t>В покое светло-зелёная в рамке: подложка c-g-50, рамка c-g-300, надпись c-g-800. Включённая — заливная, градиент c-g-700 → c-g-500, белая надпись и зелёная тень. При наведении обе темнеют на шаг.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Размеры</t>
+        </is>
+      </c>
+      <c r="B454" s="229" t="inlineStr">
+        <is>
+          <t>От кнопок отчёта: высота 72, радиус блока, надпись 17. Значок-искра слева от текста, цвет наследует от надписи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Пояснение</t>
+        </is>
+      </c>
+      <c r="B455" s="229" t="inlineStr">
+        <is>
+          <t>Вынесено из кнопки наружу, под неё. Появляется только когда подбор включён. Последняя фраза переписана: «Нажмите ещё раз, чтобы выбрать режим самостоятельно» — галочки на экране больше нет, снимать нечего.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Убрано</t>
+        </is>
+      </c>
+      <c r="B456" s="229" t="inlineStr">
+        <is>
+          <t>Классы .autobox и .autotax вместе с правилами, три устаревших комментария подряд от прежних версий блока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B457" s="229" t="inlineStr">
+        <is>
+          <t>Нажатие по кнопке включает и выключает подбор, оба поля выбора блокируются и разблокируются. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>АВТОПОДБОР: ДОВОДКА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B459" s="229" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Надпись</t>
+        </is>
+      </c>
+      <c r="B460" s="229" t="inlineStr">
+        <is>
+          <t>«Подобрать» → «Подбирать режим автоматически»: подбор идёт постоянно, при каждом изменении цифр, а не один раз по нажатию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Пояснение видно всегда</t>
+        </is>
+      </c>
+      <c r="B461" s="229" t="inlineStr">
+        <is>
+          <t>Раньше показывалось только при включённом подборе — человек не понимал, что даст кнопка, пока не нажмёт. Теперь стоит под кнопкой в обоих состояниях, класс .off и его переключение в скрипте убраны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Текст пояснения</t>
+        </is>
+      </c>
+      <c r="B462" s="229" t="inlineStr">
+        <is>
+          <t>Последняя фраза заменена: вместо «Нажмите ещё раз, чтобы выбрать режим самостоятельно» — «Режим будет меняться сам, когда меняются ваши цифры, — уведомлять о каждой смене не станем». Так человек заранее знает, что уведомлений не будет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Уведомление о смене</t>
+        </is>
+      </c>
+      <c r="B463" s="229" t="inlineStr">
+        <is>
+          <t>При включённом подборе полоса о переключении на ИП не показывается: человек сам согласился, что режим меняется без спроса. Выключил подбор — полоса возвращается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Воздух</t>
+        </is>
+      </c>
+      <c r="B464" s="229" t="inlineStr">
+        <is>
+          <t>Отступ пояснения снизу 8, у черты .exc сверху 22 и отбивка 18 вместо 18 и 16 — текст больше не липнет к линии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="B465" s="229" t="inlineStr">
+        <is>
+          <t>Подбор выключен и доход задран — полоса есть. Включили подбор — полоса ушла. Выключили — вернулась. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ЕДИНОЕ УВЕДОМЛЕНИЕ В ФОРМАХ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B467" s="229" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Было три вида</t>
+        </is>
+      </c>
+      <c r="B468" s="229" t="inlineStr">
+        <is>
+          <t>.taxoff — серая рамка, .ownnote — простой текст без подложки, .lim — плашка с круглым значком «!». Каждое выглядело по-своему.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Стало одно</t>
+        </is>
+      </c>
+      <c r="B469" s="229" t="inlineStr">
+        <is>
+          <t>Класс .fnote: жёлтая рамка c-a-200, подложка c-a-50, текст c-a-800, радиус 12, без значка. .lim приведён к нему же — круглый значок убран. .ownnote и .taxoff как отдельные правила удалены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Где применяется</t>
+        </is>
+      </c>
+      <c r="B470" s="229" t="inlineStr">
+        <is>
+          <t>«Работаю без оформления» в блоке налогов · «Живу в своём, ипотеки нет» в рабочем месте · «Не учитывать упущенную выгоду» в обучении · плашка о лимите налогового режима.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Новое уведомление</t>
+        </is>
+      </c>
+      <c r="B471" s="229" t="inlineStr">
+        <is>
+          <t>Под «Не учитывать упущенную выгоду» его не было вовсе. Написано: упущенная выгода — деньги, которые вы не заработали, пока учились; во время курса вы не снимали и не получали дохода; обычно её тоже закладывают в стоимость обучения, ведь потрачены и деньги, и рабочее время; если снять галочку, в расчёт войдёт только цена самих курсов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ВОЗВРАТ ЗНАЧЕНИЙ ПО БЛОКАМ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B472" s="229" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B473" s="229" t="inlineStr">
+        <is>
+          <t>Строчка стояла под каждым числовым полем — 21 штука, и только у них. У таблиц расходов, ползунков, переключателей и налогового блока возврата не было вовсе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="B474" s="229" t="inlineStr">
+        <is>
+          <t>Одна строка на карточку, внизу перед «не учитывать этот блок». 20 карточек — 20 строк. Возвращает всё содержимое блока: поля, ползунки, переключатели, галочки и строки таблиц расходов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Как определяет изменения</t>
+        </is>
+      </c>
+      <c r="B475" s="229" t="inlineStr">
+        <is>
+          <t>Снимок всех input и select карточки снимается при загрузке, уже после заполнения таблиц из CAT. Сравнение идёт и по числу элементов — так ловятся добавленные и удалённые строки таблиц.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Что делает при возврате</t>
+        </is>
+      </c>
+      <c r="B476" s="229" t="inlineStr">
+        <is>
+          <t>Таблицы пересобирает заново из CAT, полям возвращает значения из снимка, затем рассылает события change и input — чтобы подтянулись состояния, которые ведёт скрипт: подсветка выбора, скрытые подблоки, рамки резервов, заливка ползунков и уведомления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B477" s="229" t="inlineStr">
+        <is>
+          <t>20 строк на 20 карточек, на старте ни одна не видна. Правка дохода — появилась в блоке 01. Галочка резерва — в блоке 18. Удаление строки таблицы — в блоке 09, после возврата строк снова 10. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>ПЕРЕХОД ИЗ ОТЧЁТА ВКЛЮЧАЕТ БЛОК, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B479" s="229" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Что было</t>
+        </is>
+      </c>
+      <c r="B480" s="229" t="inlineStr">
+        <is>
+          <t>Кнопки отчёта «Заложить фонд развития» и «Заложить запас на скидку» вели на calc.html#fund_on и #disc_on. Браузер просто прокручивал к галочке — человек нажимал кнопку с ясным намерением, а дальше должен был искать и ставить галочку сам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Что стало</t>
+        </is>
+      </c>
+      <c r="B481" s="229" t="inlineStr">
+        <is>
+          <t>Анкета читает якорь и сама включает галочку, если она снята. Дальше карточка подсвечивается зелёной обводкой на 2,6 секунды и прокручивается к центру экрана — видно, что именно изменилось.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Какие якоря работают</t>
+        </is>
+      </c>
+      <c r="B482" s="229" t="inlineStr">
+        <is>
+          <t>fund_on, disc_on, fm_on, tax_auto. Список закрытый: включать что попало по адресу нельзя. Работает и при загрузке страницы, и при смене якоря на открытой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Если галочка уже стоит</t>
+        </is>
+      </c>
+      <c r="B483" s="229" t="inlineStr">
+        <is>
+          <t>Ничего не трогаем — снимать её было бы неожиданно. Только подсветка и прокрутка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B484" s="229" t="inlineStr">
+        <is>
+          <t>Все три якоря включают галочку, рамка резерва сразу зеленеет, подсветка появляется. Повторный переход при включённой галочке её не снимает. В расчёте: с #disc_on discP = 0,15, ставка выросла с 9 874 до 11 944. Без якоря расчёт не изменился.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485"/>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>СТРОКА ВОЗВРАТА ВИДНА ВСЕГДА, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B486" s="229" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>В чём была ошибка</t>
+        </is>
+      </c>
+      <c r="B487" s="229" t="inlineStr">
+        <is>
+          <t>Строка существовала во всех 20 блоках, но правило .rst держало display:none и показывалось только по классу .on — то есть после того, как человек что-то изменит. При открытии анкеты её не было видно ни в одном блоке, поэтому функция выглядела несделанной.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Что исправлено</t>
+        </is>
+      </c>
+      <c r="B488" s="229" t="inlineStr">
+        <is>
+          <t>Строка видна всегда. Пока в блоке ничего не меняли — приглушена и не нажимается через disabled. Изменили — становится обычной ссылкой. Так человек заранее видит, что откатить блок можно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Место строки</t>
+        </is>
+      </c>
+      <c r="B489" s="229" t="inlineStr">
+        <is>
+          <t>Раньше всегда падала в конец карточки. Теперь в простых блоках стоит сразу под полем: «заголовок — описание — поле — строка». Если ниже есть таблица, галочки или рамка резерва, остаётся перед «не учитывать этот блок» — иначе разорвала бы блок посередине.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B490" s="229" t="inlineStr">
+        <is>
+          <t>20 строк на 20 карточек, все видны при открытии, все неактивны. После правки дохода строка в блоке 01 стала активной. Расчёт не изменился: ноль расхождений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>СТРОКА ВОЗВРАТА: ДВЕ ПРАВКИ, 10.08.2026</t>
+        </is>
+      </c>
+      <c r="B492" s="229" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Вставала сбоку</t>
+        </is>
+      </c>
+      <c r="B493" s="229" t="inlineStr">
+        <is>
+          <t>У .rst стояло display:inline-block — в блоках расходов строка прилипала справа к кнопке «+ Добавить позицию». Заменено на display:block с width:fit-content: теперь всегда с новой строки, но подчёркивание по длине текста, а не во всю ширину.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Не видела строк таблиц</t>
+        </is>
+      </c>
+      <c r="B494" s="229" t="inlineStr">
+        <is>
+          <t>Удаление и добавление строки вызывали recalc(), но не событие DOM — проверка изменений о них не знала и строка оставалась приглушённой. Теперь обработчики .del и [data-add] шлют change с bubbles:true, по нему строка оживает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Проверено в браузере</t>
+        </is>
+      </c>
+      <c r="B495" s="229" t="inlineStr">
+        <is>
+          <t>Удалили строку в «Съёмочной технике» — строка возврата ожила, нажали — вернулось 10 строк из 9, строка снова приглушена. Добавили строку в «Офисной технике» — ожила. Расчёт не изменился: ноль расхождений.</t>
         </is>
       </c>
     </row>

--- a/Калькулятор_ставки_часа.xlsx
+++ b/Калькулятор_ставки_часа.xlsx
@@ -99,7 +99,6 @@
     <definedName name="edu_cost">'02_Параметры'!$C$76</definedName>
     <definedName name="edu_months">'02_Параметры'!$C$77</definedName>
     <definedName name="edu_life">'02_Параметры'!$C$78</definedName>
-    <definedName name="edu_mode">'02_Параметры'!$C$79</definedName>
     <definedName name="edu_opportunity">'02_Параметры'!$C$80</definedName>
     <definedName name="dep_education">'02_Параметры'!$C$81</definedName>
     <definedName name="site_mode">'02_Параметры'!$C$82</definedName>
@@ -160,7 +159,7 @@
     <definedName name="equip_only">'02_Параметры'!$C$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'09_Тексты'!$A$4:$C$514</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -3656,7 +3655,7 @@
       </c>
       <c r="D8" s="233" t="inlineStr">
         <is>
-          <t>Печать. Имя файла: ГГГГ-ММ-ДД Счетикс для фотографа</t>
+          <t>Печать. Имя файла: ГГГГ-ММ-ДД Счётикс для фотографа</t>
         </is>
       </c>
       <c r="E8" s="234" t="inlineStr">
@@ -4195,7 +4194,7 @@
       </c>
       <c r="D27" s="233" t="inlineStr">
         <is>
-          <t>Знак сверху, «счетикс» под ним</t>
+          <t>Знак сверху, «счётикс» под ним</t>
         </is>
       </c>
       <c r="E27" s="234" t="inlineStr">
@@ -4974,7 +4973,7 @@
       </c>
       <c r="C10" s="113" t="inlineStr">
         <is>
-          <t>Ваш доход</t>
+          <t>Ваш желаемый доход</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5069,7 @@
       </c>
       <c r="C18" s="113" t="inlineStr">
         <is>
-          <t>Налоговый режим</t>
+          <t>Ваш налоговый режим</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5117,7 @@
       </c>
       <c r="C22" s="113" t="inlineStr">
         <is>
-          <t>От него зависят ставка налога и страховые взносы.</t>
+          <t>Выберите свой режим налогообложения или воспользуйтесь автоматическим подбором.</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5151,7 @@
       </c>
       <c r="C24" s="113" t="inlineStr">
         <is>
-          <t>От этого зависит ставка НПД: 4% с частных лиц, 6% с компаний и ИП. Нужно, чтобы в сравнении режимов показать только те варианты, которые вам подходят.</t>
+          <t>Если работаете и с частными лицами, и с компаниями — НПД посчитаем по усреднённой ставке 5%.</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5257,7 @@
       </c>
       <c r="C32" s="113" t="inlineStr">
         <is>
-          <t>Как мы считаем</t>
+          <t>Как мы считаем:</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5281,7 @@
       </c>
       <c r="C34" s="113" t="inlineStr">
         <is>
-          <t>Мы считаем по норме</t>
+          <t>Человеческие условия</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5305,7 @@
       </c>
       <c r="C36" s="113" t="inlineStr">
         <is>
-          <t>официальные условия труда, признанные государством нормой</t>
+          <t>Официальные нормы труда и отдыха, установленные государством.</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5353,7 @@
       </c>
       <c r="C40" s="113" t="inlineStr">
         <is>
-          <t>и один больничный — болеть никто не планирует, но мы заложили</t>
+          <t>И один больничный — чтобы спокойно восстановиться без страха потерять доход.</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5377,7 @@
       </c>
       <c r="C42" s="113" t="inlineStr">
         <is>
-          <t>Рабочая неделя</t>
+          <t>Комфортный распорядок</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5401,7 @@
       </c>
       <c r="C44" s="113" t="inlineStr">
         <is>
-          <t>восемь часов в день, как у всех</t>
+          <t>И 8-часовой рабочий день — норма труда, установленная законом.</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5512,7 @@
       </c>
       <c r="C52" s="113" t="inlineStr">
         <is>
-          <t>От скольких часов вы выезжаете на заказ. Это ваш минимум — от него считается базовая стоимость часа, а всё, что длиннее, идёт со скидкой за объём.</t>
+          <t>Укажите минимальное количество съёмочных часов, ради которых вы готовы выезжать на заказ.</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5642,7 @@
       </c>
       <c r="C62" s="113" t="inlineStr">
         <is>
-          <t>Загрузка и выгрузка файлов, отбор кадров, цветокоррекция, ретушь, структурирование архива, подготовка к сдаче.</t>
+          <t>Укажите, сколько времени в среднем вы тратите на подготовку материала за 1 час съёмки. Учитывайте всё время — от начала выгрузки материала на компьютер до передачи готового результата клиенту.</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5719,7 @@
       </c>
       <c r="C68" s="113" t="inlineStr">
         <is>
-          <t>Показ референсов, обсуждение деталей и сроков, согласование правок, организационные вопросы по съёмке.</t>
+          <t>Укажите, сколько времени в среднем вы тратите на общение с клиентом и организацию одного уже подтверждённого проекта.</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5796,7 @@
       </c>
       <c r="C74" s="113" t="inlineStr">
         <is>
-          <t>Съёмка и монтаж рилс, ведение соцсетей, отклики на площадках, общение в чатах и другие способы поиска заказов.</t>
+          <t>Укажите, сколько времени в среднем вы тратите на поиск новых клиентов и продвижение своих услуг.</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5868,8 @@
       </c>
       <c r="C80" s="113" t="inlineStr">
         <is>
-          <t>Всё, без чего невозможно провести съёмку. Укажите текущую рыночную стоимость и срок, за который вещь придётся заменить</t>
+          <t>Это набор вашего базового оборудования, без которого вы просто не сможете провести съёмку. Укажите текущую рыночную стоимость и срок, за который позицию придётся заменить.
+Не включайте сюда специфическое оборудование, которое требуется под задачи конкретного заказчика. Его стоимость лучше сразу закладывать в смету как дополнительную аренду.</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="C90" s="113" t="inlineStr">
         <is>
-          <t>Компьютер и всё, на чём вы обрабатываете материал и ведёте дела вне площадки</t>
+          <t>Это оборудование, которое помогает вам выполнять заказы и решать рабочие задачи за компьютером. Укажите его текущую рыночную стоимость и срок, через который планируете заменить.</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C102" s="113" t="inlineStr">
         <is>
-          <t>Сервисы, за которые вы платите регулярно: облако, редакторы, планировщики.</t>
+          <t>Лицензии и сервисы, за которые вы регулярно платите.</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C112" s="113" t="inlineStr">
         <is>
-          <t>Программы и плагины, купленные один раз. Со временем устаревают, поэтому распределяем стоимость на срок использования.</t>
+          <t>Программы и лицензии, которые вы оплачивали один раз и используете длительное время.</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="C122" s="113" t="inlineStr">
         <is>
-          <t>Дома считаем только долю метров под кабинет, арендованное помещение — целиком</t>
+          <t>В найме рабочее место предоставляет работодатель. Когда вы работаете на себя, вы создаёте и оплачиваете его самостоятельно — поэтому эти расходы тоже должны быть учтены в стоимости вашего часа.</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C126" s="113" t="inlineStr">
         <is>
-          <t>Аренда или платёж по ипотеке. В расчёт войдёт только доля, приходящаяся на рабочую зону.</t>
+          <t>Аренда или ипотека.</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C134" s="113" t="inlineStr">
         <is>
-          <t>Учитываются полностью: без света и интернета работать невозможно.</t>
+          <t>Если вы работаете из дома, коммунальные платежи, интернет и связь учитываются пропорционально площади, которую занимает рабочая зона.</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="C142" s="113" t="inlineStr">
         <is>
-          <t>Сколько метров занимает рабочая зона?</t>
+          <t>Сколько метров выделено под вашу рабочую зону?</t>
         </is>
       </c>
     </row>
@@ -6679,11 +6679,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C144" s="113" t="inlineStr">
-        <is>
-          <t>Стол, техника, место для хранения оборудования и съёмочный уголок, если он есть.</t>
-        </is>
-      </c>
+      <c r="C144" s="113" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -6753,7 +6749,7 @@
       </c>
       <c r="C150" s="113" t="inlineStr">
         <is>
-          <t>Студия, кабинет или место в коворкинге. Учитывается полностью.</t>
+          <t>Студия, кабинет или место в коворкинге.</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6845,7 @@
       </c>
       <c r="C158" s="113" t="inlineStr">
         <is>
-          <t>Обустройство рабочего пространства</t>
+          <t>Обустройство рабочего места</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6869,8 @@
       </c>
       <c r="C160" s="113" t="inlineStr">
         <is>
-          <t>Опишите разовые вложения в организацию рабочего места: мебель, ремонт, освещение, полки для техники. Даже если это уголок в квартире — эти деньги вы потратили, чтобы иметь возможность работать.</t>
+          <t>Укажите разовые вложения в создание и обустройство рабочего места.
+Если вы делали всё самостоятельно, рекомендуем использовать в расчёте сумму, которую пришлось бы заплатить наёмным специалистам за аналогичную работу, и общую стоимость закупленных материалов.</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7158,7 @@
       </c>
       <c r="C182" s="113" t="inlineStr">
         <is>
-          <t>Стоимость распределится равномерно на этот срок. Обычно берут от 5 до 10 лет.</t>
+          <t>Стоимость обучения будет равномерно распределена на выбранный срок. Обычно для расчёта берут период от 5 до 10 лет.</t>
         </is>
       </c>
     </row>
@@ -7231,11 +7228,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C188" s="113" t="inlineStr">
-        <is>
-          <t>Если делали сами — это тоже вложение: вы потратили время вместо работы по профессии</t>
-        </is>
-      </c>
+      <c r="C188" s="113" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -7257,7 +7250,7 @@
       </c>
       <c r="C190" s="113" t="inlineStr">
         <is>
-          <t>Сколько вы заплатили за сайт?</t>
+          <t>Сколько вы заплатили за создание сайта?</t>
         </is>
       </c>
     </row>
@@ -7279,11 +7272,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C192" s="113" t="inlineStr">
-        <is>
-          <t>Разработка, дизайн, наполнение — всё, что оплачивали подрядчику.</t>
-        </is>
-      </c>
+      <c r="C192" s="113" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -7305,7 +7294,7 @@
       </c>
       <c r="C194" s="113" t="inlineStr">
         <is>
-          <t>Сколько часов вы потратили на сайт?</t>
+          <t>Сколько времени вы потратили на создание сайта?</t>
         </is>
       </c>
     </row>
@@ -7327,11 +7316,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C196" s="113" t="inlineStr">
-        <is>
-          <t>Считаем по вашей же ставке рабочего часа: это время вы могли бы отдать съёмкам.</t>
-        </is>
-      </c>
+      <c r="C196" s="113" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -7473,7 +7458,7 @@
       </c>
       <c r="C208" s="113" t="inlineStr">
         <is>
-          <t>Деньги, которые вы платите за привлечение клиентов</t>
+          <t>Деньги, которые вы регулярно тратите на поиск и привлечение клиентов</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7614,7 @@
       </c>
       <c r="C220" s="113" t="inlineStr">
         <is>
-          <t>Обслуживание расчётного счёта, уведомления и прочие фиксированные списания.</t>
+          <t>Платежи за банковское обслуживание и услуги, которые оплачиваются в фиксированной сумме.</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7722,7 @@
       </c>
       <c r="C228" s="113" t="inlineStr">
         <is>
-          <t>Комиссия с каждой оплаты</t>
+          <t>Комиссии банка</t>
         </is>
       </c>
     </row>
@@ -7761,21 +7746,21 @@
       </c>
       <c r="C230" s="113" t="inlineStr">
         <is>
-          <t>Какая у вас ставка эквайринга?</t>
+          <t>Эквайринг</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>Пояснение к вопросу</t>
+          <t>Пояснение к секции</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="27" t="inlineStr">
         <is>
-          <t>qd_17</t>
+          <t>shd_06</t>
         </is>
       </c>
       <c r="B232" s="112" t="inlineStr">
@@ -7785,7 +7770,7 @@
       </c>
       <c r="C232" s="113" t="inlineStr">
         <is>
-          <t>Процент, который банк удерживает при оплате картой или по QR-коду.</t>
+          <t>Плата, которую взимает банк в виде процента от суммы произведённой операции.</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7794,7 @@
       </c>
       <c r="C234" s="113" t="inlineStr">
         <is>
-          <t>Какая доля клиентов платит безналично?</t>
+          <t>Какая доля оплат проходит через эквайринг?</t>
         </is>
       </c>
     </row>
@@ -7831,11 +7816,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C236" s="113" t="inlineStr">
-        <is>
-          <t>Если часть заказов оплачивают переводом без комиссии — уменьшите значение.</t>
-        </is>
-      </c>
+      <c r="C236" s="113" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -7879,11 +7860,7 @@
           <t>Форма · вопросы анкеты</t>
         </is>
       </c>
-      <c r="C240" s="113" t="inlineStr">
-        <is>
-          <t>Либо тратите своё время, либо платите специалисту</t>
-        </is>
-      </c>
+      <c r="C240" s="113" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -7929,7 +7906,23 @@
       </c>
       <c r="C244" s="113" t="inlineStr">
         <is>
-          <t>Подготовка деклараций, уплата взносов, сверка с налоговой, ведение книги учёта.</t>
+          <t>Вот что мы заложили как основные этапы ведения учёта и бухгалтерии
+1. Учёт доходов и расходов:
+— фиксация доходов и расходов;
+— ведение книги учёта;
+— сверка операций с банковской выпиской.
+2. Налоги и взносы:
+— расчёт налогов;
+— уплата налогов и страховых взносов;
+— контроль сроков обязательных платежей.
+3. Подготовка отчётности:
+— подготовка и отправка деклараций;
+— подготовка другой обязательной отчётности;
+— контроль сроков сдачи.
+4. Взаимодействие с налоговой:
+— сверка с налоговой инспекцией;
+— проверка начислений и задолженности;
+— ответы на требования и уведомления.</t>
         </is>
       </c>
     </row>
@@ -9457,12 +9450,12 @@
       </c>
       <c r="C344" s="113" t="inlineStr">
         <is>
-          <t>счетикс</t>
+          <t>счётикс</t>
         </is>
       </c>
       <c r="H344" s="297" t="inlineStr">
         <is>
-          <t>УДАЛЕНО из HTML: слово «счетикс» в знаке выводится без ключа — как в отчёте, 10.08.2026</t>
+          <t>УДАЛЕНО из HTML: слово «счётикс» в знаке выводится без ключа — как в отчёте, 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9511,9 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Лишних денег вы не тратите, но отдаёте клиентам свои метры бесплатно — любой бизнес закладывает место в цену.</t>
+          <t>Рекомендуем учитывать стоимость рабочего места в расчёте.
+Иначе вы фактически субсидируете клиентов своими метрами, используя собственное жильё как рабочий ресурс для выполнения их задач.
+Укажите актуальную стоимость аренды аналогичного жилья в вашем городе или размер ежемесячного ипотечного платежа.</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11724,7 @@
       </c>
       <c r="C474" s="113" t="inlineStr">
         <is>
-          <t>что сюда входит</t>
+          <t>Вот что мы заложили как основные этапы постпродакшна</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11741,7 @@
       </c>
       <c r="C475" s="113" t="inlineStr">
         <is>
-          <t>что сюда входит</t>
+          <t>Вот что мы заложили как основные этапы работы с клиентом</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11758,7 @@
       </c>
       <c r="C476" s="113" t="inlineStr">
         <is>
-          <t>что сюда входит</t>
+          <t>Что включено в эти 2 часа</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12083,7 @@
       </c>
       <c r="C494" s="113" t="inlineStr">
         <is>
-          <t>В среднем, после отбора и цветокоррекции. Нужно, чтобы посчитать цену одного кадра.</t>
+          <t>Укажите, сколько готовых кадров в среднем вы отдаёте за один час съёмки, после отбора и цветокоррекции.</t>
         </is>
       </c>
     </row>
@@ -18314,7 +18309,7 @@
     <row r="112">
       <c r="A112" s="226" t="inlineStr">
         <is>
-          <t>• Замок горизонтальный: знак 46 px, справа «счетикс» 19 px с разрядкой .11em, под ним подпись 9 px.</t>
+          <t>• Замок горизонтальный: знак 46 px, справа «счётикс» 19 px с разрядкой .11em, под ним подпись 9 px.</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18323,7 @@
     <row r="114">
       <c r="A114" s="226" t="inlineStr">
         <is>
-          <t>• В подвале: знак 20 px + «счетикс» 12 px, серым, прозрачность .55.</t>
+          <t>• В подвале: знак 20 px + «счётикс» 12 px, серым, прозрачность .55.</t>
         </is>
       </c>
     </row>
@@ -19380,7 +19375,7 @@
       </c>
       <c r="B22" s="152" t="inlineStr">
         <is>
-          <t>счетикс</t>
+          <t>счётикс</t>
         </is>
       </c>
       <c r="C22" s="152" t="inlineStr">
@@ -19414,7 +19409,7 @@
       </c>
       <c r="B24" s="152" t="inlineStr">
         <is>
-          <t>счетикс</t>
+          <t>счётикс</t>
         </is>
       </c>
       <c r="C24" s="152" t="inlineStr">
@@ -19492,7 +19487,7 @@
       </c>
       <c r="C30" s="231" t="inlineStr">
         <is>
-          <t>&lt;div class="brand" title="Счетикс — твоя юнит-экономика"&gt;&lt;span class="btx"&gt;&lt;span class="bt"&gt;счетикс&lt;/span&gt;&lt;span class="bd" data-t="bt_02"&gt;&lt;i&gt;т&lt;/i&gt;&lt;i&gt;в&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;я&lt;/i&gt;&lt;i&gt;&amp;nbsp;&lt;/i&gt;&lt;i&gt;ю&lt;/i&gt;&lt;i&gt;н&lt;/i&gt;&lt;i&gt;и&lt;/i&gt;&lt;i&gt;т&lt;/i&gt;&lt;i&gt;-&lt;/i&gt;&lt;i&gt;э&lt;/i&gt;&lt;i&gt;к&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;н&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;м&lt;/i&gt;&lt;i&gt;и&lt;/i&gt;&lt;i&gt;к&lt;/i&gt;&lt;i&gt;а&lt;/i&gt;&lt;/span&gt;&lt;/span&gt;&lt;svg class="bx" viewBox="0 0 32 32" fill="none" aria-hidden="true"&gt;&lt;rect x="10.95" y="2.09" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 7.14)" fill="var(--c-ln)"/&gt;&lt;rect x="19.81" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 24.86 16)" fill="var(--c-g-500)"/&gt;&lt;rect x="10.95" y="19.81" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 24.86)" fill="var(--c-ln)"/&gt;&lt;rect x="2.09" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 7.14 16)" fill="var(--c-ln)"/&gt;&lt;/svg&gt;&lt;/div&gt;</t>
+          <t>&lt;div class="brand" title="Счётикс — твоя юнит-экономика"&gt;&lt;span class="btx"&gt;&lt;span class="bt"&gt;счётикс&lt;/span&gt;&lt;span class="bd" data-t="bt_02"&gt;&lt;i&gt;т&lt;/i&gt;&lt;i&gt;в&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;я&lt;/i&gt;&lt;i&gt;&amp;nbsp;&lt;/i&gt;&lt;i&gt;ю&lt;/i&gt;&lt;i&gt;н&lt;/i&gt;&lt;i&gt;и&lt;/i&gt;&lt;i&gt;т&lt;/i&gt;&lt;i&gt;-&lt;/i&gt;&lt;i&gt;э&lt;/i&gt;&lt;i&gt;к&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;н&lt;/i&gt;&lt;i&gt;о&lt;/i&gt;&lt;i&gt;м&lt;/i&gt;&lt;i&gt;и&lt;/i&gt;&lt;i&gt;к&lt;/i&gt;&lt;i&gt;а&lt;/i&gt;&lt;/span&gt;&lt;/span&gt;&lt;svg class="bx" viewBox="0 0 32 32" fill="none" aria-hidden="true"&gt;&lt;rect x="10.95" y="2.09" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 7.14)" fill="var(--c-ln)"/&gt;&lt;rect x="19.81" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 24.86 16)" fill="var(--c-g-500)"/&gt;&lt;rect x="10.95" y="19.81" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 24.86)" fill="var(--c-ln)"/&gt;&lt;rect x="2.09" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 7.14 16)" fill="var(--c-ln)"/&gt;&lt;/svg&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19504,7 @@
       </c>
       <c r="C31" s="231" t="inlineStr">
         <is>
-          <t>&lt;span class="lgs" title="Счетикс — твоя юнит-экономика"&gt;&lt;span class="lt"&gt;счетикс&lt;/span&gt;&lt;svg class="lx" viewBox="0 0 32 32" fill="none" aria-hidden="true"&gt;&lt;rect x="10.95" y="2.09" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 7.14)" fill="var(--c-ln)"/&gt;&lt;rect x="19.81" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 24.86 16)" fill="var(--c-g-500)"/&gt;&lt;rect x="10.95" y="19.81" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 24.86)" fill="var(--c-ln)"/&gt;&lt;rect x="2.09" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 7.14 16)" fill="var(--c-ln)"/&gt;&lt;/svg&gt;&lt;/span&gt;&lt;/span&gt;</t>
+          <t>&lt;span class="lgs" title="Счётикс — твоя юнит-экономика"&gt;&lt;span class="lt"&gt;счётикс&lt;/span&gt;&lt;svg class="lx" viewBox="0 0 32 32" fill="none" aria-hidden="true"&gt;&lt;rect x="10.95" y="2.09" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 7.14)" fill="var(--c-ln)"/&gt;&lt;rect x="19.81" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 24.86 16)" fill="var(--c-g-500)"/&gt;&lt;rect x="10.95" y="19.81" width="10.10" height="10.10" rx="1.90" transform="rotate(45 16 24.86)" fill="var(--c-ln)"/&gt;&lt;rect x="2.09" y="10.95" width="10.10" height="10.10" rx="1.90" transform="rotate(45 7.14 16)" fill="var(--c-ln)"/&gt;&lt;/svg&gt;&lt;/span&gt;&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19562,7 @@
     <row r="41">
       <c r="A41" s="226" t="inlineStr">
         <is>
-          <t>• В подвале обоих файлов знак стоит СВЕРХУ, надпись «счетикс» — под ним.</t>
+          <t>• В подвале обоих файлов знак стоит СВЕРХУ, надпись «счётикс» — под ним.</t>
         </is>
       </c>
     </row>
@@ -19816,7 +19811,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>«счетикс»</t>
+          <t>«счётикс»</t>
         </is>
       </c>
       <c r="C75" s="275" t="inlineStr">
@@ -22352,7 +22347,7 @@
       </c>
       <c r="E38" s="275" t="inlineStr">
         <is>
-          <t>Блок 02. Текст начинается там же, где плашки дней: 58px (колонка часов) + 7px (зазор сетки) = 65px. Отступ карточки прибавлять НЕ нужно — плашка уже внутри неё. Знак «Счетикс»: 150px, left −58px, top −58px, прозрачность 6%, уходит в левый верхний угол под градиент, текст не перекрывает. Знак рисуется в JS вместе с текстом — innerHTML затирает разметку</t>
+          <t>Блок 02. Текст начинается там же, где плашки дней: 58px (колонка часов) + 7px (зазор сетки) = 65px. Отступ карточки прибавлять НЕ нужно — плашка уже внутри неё. Знак «Счётикс»: 150px, left −58px, top −58px, прозрачность 6%, уходит в левый верхний угол под градиент, текст не перекрывает. Знак рисуется в JS вместе с текстом — innerHTML затирает разметку</t>
         </is>
       </c>
     </row>
@@ -22615,7 +22610,7 @@
       </c>
       <c r="E58" s="229" t="inlineStr">
         <is>
-          <t>Блок 02. Текст начинается там же, где плашки дней: 58px (колонка часов) + 7px (зазор сетки) = 65px. Отступ карточки прибавлять НЕ нужно — плашка уже внутри неё. Знак «Счетикс»: 150px, left −58px, top −58px, прозрачность 6%, уходит в левый верхний угол под градиент, текст не перекрывает. Знак рисуется в JS вместе с текстом — innerHTML затирает разметку</t>
+          <t>Блок 02. Текст начинается там же, где плашки дней: 58px (колонка часов) + 7px (зазор сетки) = 65px. Отступ карточки прибавлять НЕ нужно — плашка уже внутри неё. Знак «Счётикс»: 150px, left −58px, top −58px, прозрачность 6%, уходит в левый верхний угол под градиент, текст не перекрывает. Знак рисуется в JS вместе с текстом — innerHTML затирает разметку</t>
         </is>
       </c>
     </row>
@@ -22663,7 +22658,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Крест 3×3: плашка сверху, справа, снизу, слева, знак «Счетикс» в середине. На широком экране по бокам оставалось много пустого поля.</t>
+          <t>Крест 3×3: плашка сверху, справа, снизу, слева, знак «Счётикс» в середине. На широком экране по бокам оставалось много пустого поля.</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23920,7 @@
       </c>
       <c r="B196" s="229" t="inlineStr">
         <is>
-          <t>Взят из отчёта целиком: знак с растянутой подписью «твоя юнит-экономика» и под ним реквизиты .fcop. Был маленький значок со словом «счетикс» в одну строку.</t>
+          <t>Взят из отчёта целиком: знак с растянутой подписью «твоя юнит-экономика» и под ним реквизиты .fcop. Был маленький значок со словом «счётикс» в одну строку.</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24008,7 @@
       </c>
       <c r="B206" s="229" t="inlineStr">
         <is>
-          <t>Блок 15 «Фонд развития» и блок 16 «Запас на скидку», у каждого свой заголовок и подзаголовок. Внутри — прежняя рамка .zap со своей галочкой.</t>
+          <t>Блок 15 «Фонд развития» и блок 16 «Запас на скидку», у каждого свой заголовок и подзаголовок. Внутри — прежняя рамка .zap со своей галочкой. Тексты блока «Запас на скидку»: «Чтобы гибко настраивать программу лояльности и не терять в доходе» и «Без запаса на скидку ваши возможности будут сильно ограничены: вы сможете давать скидки только за объём и в небольшом размере».</t>
         </is>
       </c>
     </row>
@@ -24229,7 +24224,7 @@
       </c>
       <c r="B228" s="229" t="inlineStr">
         <is>
-          <t>Два ромба «Счетикс» лежат фоном внутри кнопки: крупный слева заходит за край, поменьше справа. Приём и прозрачности взяты у .hdeco — фонового знака в шапке отчёта: .07 и .09. Надпись и значок лежат выше по слою, знак им не мешает.</t>
+          <t>Два ромба «Счётикс» лежат фоном внутри кнопки: крупный слева заходит за край, поменьше справа. Приём и прозрачности взяты у .hdeco — фонового знака в шапке отчёта: .07 и .09. Надпись и значок лежат выше по слою, знак им не мешает.</t>
         </is>
       </c>
     </row>
@@ -24273,7 +24268,7 @@
       </c>
       <c r="B232" s="229" t="inlineStr">
         <is>
-          <t>У .exc галочка красная, c-r-500. Пока флажок стоит, подпись тоже красная, c-r-700, и полужирная — сразу видно, какие блоки изъяты. Галочки .flag внутри карточек не тронуты: они работают на включение и остаются зелёными.</t>
+          <t>У .exc галочка красная, c-r-500. Пока флажок стоит, подпись тоже красная, c-r-700, и полужирная — сразу видно, какие блоки изъяты. Галочки .flag внутри карточек не тронуты: они работают на включение и остаются зелёными. У всех исключённых карточек фон остаётся без изменений; только содержимое приглушается до opacity 0,65. Нижняя строка с активной галочкой остаётся полностью контрастной. Жёлтое предупреждение налогового блока при этом не приглушается.</t>
         </is>
       </c>
     </row>
@@ -24409,7 +24404,7 @@
       </c>
       <c r="B246" s="229" t="inlineStr">
         <is>
-          <t>Вынесена в отдельный блок 03 с подзаголовком «С ней мы сравним расчётную — чтобы вы увидели разницу в год и в месяц». Вопрос, подсказка и поле перенесены дословно.</t>
+          <t>Блок 03 «Ваша текущая ставка» получил подзаголовок: «Увидите, сколько вы зарабатываете сейчас, и сравните с желаемым доходом.» Поле current_rate и расчёт не изменены.</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24588,7 @@
       </c>
       <c r="B264" s="229" t="inlineStr">
         <is>
-          <t>«Вернуть значения по умолчанию». Не «сбросить» и не «очистить»: поля не опустеют, а вернутся к нашим исходным цифрам — надпись должна обещать именно это.</t>
+          <t>Локальная подсказка у иконки отката: «Вернуть значение по умолчанию». Общая кнопка всей анкеты сохраняет множественное число, поскольку возвращает сразу все поля.</t>
         </is>
       </c>
     </row>
@@ -24673,7 +24668,7 @@
       </c>
       <c r="B272" s="229" t="inlineStr">
         <is>
-          <t>Во весь первый экран: ромб от 150 до 300 px, слово «счетикс» до 104 px. Размеры вяжутся к высоте окна через clamp и vh, а не к ширине — иначе на ноутбуке знак не влезал бы в экран.</t>
+          <t>Во весь первый экран: ромб от 150 до 300 px, слово «счётикс» до 104 px. Размеры вяжутся к высоте окна через clamp и vh, а не к ширине — иначе на ноутбуке знак не влезал бы в экран.</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25212,7 @@
       </c>
       <c r="B328" s="229" t="inlineStr">
         <is>
-          <t>У знака теперь role=img и aria-label «Счетикс» вместо aria-hidden: он перестал быть чисто декоративным, раз с ним взаимодействуют.</t>
+          <t>У знака теперь role=img и aria-label «Счётикс» вместо aria-hidden: он перестал быть чисто декоративным, раз с ним взаимодействуют.</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25244,7 @@
       </c>
       <c r="B332" s="229" t="inlineStr">
         <is>
-          <t>Знак на входе занимает почти весь экран: снизу к нему вплотную примыкает слово «счетикс», сверху плашка вылезала за край окна. Ставить её было некуда.</t>
+          <t>Знак на входе занимает почти весь экран: снизу к нему вплотную примыкает слово «счётикс», сверху плашка вылезала за край окна. Ставить её было некуда.</t>
         </is>
       </c>
     </row>
@@ -25349,7 +25344,7 @@
       </c>
       <c r="B342" s="229" t="inlineStr">
         <is>
-          <t>Под шестью плашками: «Что значит пробный режим», три абзаца. Подложка как у плашек, но во всю ширину — это сноска ко всей странице, а не седьмое преимущество. Ключи wt_02 … wt_05.</t>
+          <t>Блок пробного режима: заголовок «СЧЁТИКС работает в пробном режиме», жёлтый треугольник с белым знаком, три абзаца о бесплатном доступе, полной работе расчётов и обратной связи по email@example.com.</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25368,7 @@
       </c>
       <c r="B344" s="229" t="inlineStr">
         <is>
-          <t>Под кнопками «Рассчитать» и «Вернуть значения», перед подвалом. Текст тот же, что на входе, оформление в песочной гамме карточки. При печати скрыт. Ключи ct_02 … ct_05.</t>
+          <t>Под кнопками «Рассчитать» и «Вернуть значения», перед подвалом. Текст тот же, что на входе, оформление в песочной гамме карточки. При печати скрыт. Ключи ct_02 … ct_05. Перед логотипом в подвале добавлена отдельная разделительная линия и увеличенный вертикальный отступ.</t>
         </is>
       </c>
     </row>
@@ -25429,7 +25424,7 @@
       </c>
       <c r="B350" s="229" t="inlineStr">
         <is>
-          <t>Перед блоком 14 добавлен разделитель .sect «Теперь заложите резервы» с подзаголовком: расходы выше — то, без чего работа не состоится, резервы — запас на случившееся и на то, что хотите себе позволить; не заложите в цену — заплатите из дохода. Оформление то же, что у раздела «Как мы считаем». Ключи h2_rez и ss_rez.</t>
+          <t>Раздел «Теперь заложим резервы:» пока сохраняет прежнюю композицию: крупная галочка и текст «Отлично! Базовый минимум у нас уже есть», затем заголовок и девиз «Теперь заложим запас прочности, чтобы ваш доход сохранял стабильность в любых условиях». Добавленная ранее горизонтальная разделительная линия полностью удалена. Галочка — 82/68 px на десктопе и 56/46 px на мобильных.</t>
         </is>
       </c>
     </row>
@@ -25557,7 +25552,7 @@
       </c>
       <c r="B362" s="229" t="inlineStr">
         <is>
-          <t>На входе «Сервис работает в пробном режиме», в подсказке отчёта то же самое. В анкете короче — «Пробный режим». Заголовок блока везде «Что значит пробный режим». Слово «калькулятор» из подсказки убрано: сервис, а не калькулятор.</t>
+          <t>Единая формулировка пробного режима в анкете: «СЧЁТИКС работает в пробном режиме». Жёлтый знак используется как информационный акцент.</t>
         </is>
       </c>
     </row>
@@ -25637,7 +25632,7 @@
       </c>
       <c r="B370" s="229" t="inlineStr">
         <is>
-          <t>Анкета разбита разделителями .sect: «Как мы считаем» (было), «Теперь посчитаем расходы» (новый, перед блоком 05) и «Теперь заложите резервы» (перед блоком 14). Ключи h2_rash и ss_rash.</t>
+          <t>Анкета разбита разделителями .sect: «Как мы считаем:» (было), «Теперь посчитаем расходы» (новый, перед блоком 05) и «Теперь заложим резервы:» (перед блоком 14). Ключи h2_rash и ss_rash.</t>
         </is>
       </c>
     </row>
@@ -25925,7 +25920,7 @@
       </c>
       <c r="B398" s="229" t="inlineStr">
         <is>
-          <t>Было одной строкой с обещанием «режим можно сменить вручную» — неправда, сменить на НПД уже нельзя. Стало: заголовок «Налоговый режим переключён на ИП» отдельной строкой, ниже объяснение: доход, который вам нужен, выше нормы для самозанятых, поэтому самозанятость больше недоступна и убрана из списка; между режимами ИП выбирать можно.</t>
+          <t>При автоматической замене НПД на УСН 6% показывается мягкое жёлтое уведомление: «Налоговый режим был автоматически изменен в связи с превышением лимита предполагаемой годовой выручки». Когда данные снова укладываются в лимит НПД, режим автоматически возвращается и появляется зелёное уведомление: «Вы вернулись на НПД. Ваш лимит в порядке». Оба уведомления показываются 12 секунд, после чего мягко растворяются без смещения; крестик позволяет закрыть их раньше. Повторные пересчёты и прокрутка не перезапускают таймер.</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25932,7 @@
       </c>
       <c r="B399" s="229" t="inlineStr">
         <is>
-          <t>При автоматической смене режима вопрос «С кем вы чаще работаете» оставался на экране — обработчик change при программной смене не срабатывает. Добавлен прямой вызов ктоВидим().</t>
+          <t>Вопрос «С кем вы чаще работаете?» снова расположен после выбора налогового режима и показывается только для НПД. При НПД калькулятор внутри применяет 4% для частных лиц, 6% для компаний и ИП, 5% для смешанного варианта; пользователю дополнительную ставку выбирать не нужно.</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25988,7 @@
       </c>
       <c r="B405" s="229" t="inlineStr">
         <is>
-          <t>Заголовок «Ваша текущая ставка», подзаголовок «С ней мы сравним расчётную — чтобы вы увидели разницу в год и в месяц» и поле. Поле current_rate не тронуто, расчёт сошёлся: 60 полей, ноль расхождений.</t>
+          <t>Заголовок «Ваша текущая ставка», подзаголовок «Увидите, сколько вы зарабатываете сейчас, и сравните с желаемым доходом.» и поле current_rate.</t>
         </is>
       </c>
     </row>
@@ -26053,6 +26048,18 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ГЛАВНЫЙ БАННЕР «ПРИСТУПИМ К РАСЧЁТУ»</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>В главном баннере три коротких преимущества с иконками и компактными подложками: «Готовые списки», «Реальный опыт», «Гибкая настройка». На десктопе — три колонки без прокрутки, на мобильных — одна колонка. Эта композиция стала общей для остальных смысловых баннеров. Подписи во всех баннерных плашках принудительно оформлены ровно в две строки.</t>
+        </is>
+      </c>
+    </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
@@ -26081,7 +26088,7 @@
       </c>
       <c r="B415" s="229" t="inlineStr">
         <is>
-          <t>Раздел .sect «Структурируем ваше время» с подзаголовком в две строки, под ним пять отдельных карточек: Минимальная съёмка · Кадры с одной съёмки · Обработка материала · Общение с клиентом · Продвижение. В каждой только заголовок, подзаголовок и поле.</t>
+          <t>Раздел «Время — ваш главный рабочий ресурс». Три двухстрочные плашки: «Съёмка и / обработка» с иконкой камеры, «Работа с / клиентом» с иконкой диалога, «Поиск / заказов» с иконкой поиска. Под заголовком остаётся: «Посчитаем время, которое обычно остаётся невидимым». После плашек условий труда добавлено уведомление: «Можно ли работать больше? Конечно, если вы сами этого хотите. Дополнительные часы могут помогать быстрее расти или достигать своих целей. Но если без переработок ваша экономика не сходится, стоит пересмотреть стоимость часа: иначе вы просто создаёте себе рабочее место хуже, чем в найме. По ТК РФ сверхурочная работа оплачивается не менее чем в 1,5 раза за первые два часа и не менее чем в 2 раза за последующие. Работа в выходные и нерабочие праздничные дни — не менее чем в двойном размере.» Под ним пять отдельных карточек временных параметров. Карточки 04–08 объединены общей градиентной подложкой; фоновая иллюстрация удалена. Баннер времени проработан по логике «Приступим к расчёту»: главный заголовок набран Prata, над ним только крупная иконка часов без обводки и текста. Отдельный фоновый рисунок удалён. Цветовая гамма группы времени заменена на насыщенный синий градиент плашек «Отпуск» и «График 5/2». Карточки раздела времени получили мягкую полупрозрачную белую заливку, через которую слегка просвечивает синий фон. Блок 06 «Время на постпродакшн»: подзаголовок и поле идут первыми; затем раскрытие с шестью карточками со светло-зелёной подложкой и зелёной обводкой, градиентно-зелёными номерами с белыми цифрами, увеличенной типографикой и выровненными списками. «Ретушь не включена!» оформлено как синее информационное уведомление. Плашка о неоднозначности показателя и замере 3–5 съёмок перенесена ниже этого уведомления и оставлена нейтральной. Формула post_ratio не менялась. Числовые поля времени, кадров и сроков получили автоматическое русское склонение единиц: 1 час, 2 часа, 5 часов, 0,5 часа; 1 год, 2 года, 5 лет. Полупрозрачный белый градиент карточек сделан менее выраженным. Внешние отступы баннера времени приведены к баннеру «Приступим к расчёту»: 78/84 px и 30 px по бокам. Блок 07 переименован в «Работа с клиентом (на один проект)» и оформлен по схеме постпродакшна: три этапа в раскрытии с зелёным оформлением, синее информационное уведомление об исключённой продюсерской работе и нейтральная плашка с обоснованием; строка о замере реальных проектов перенесена сразу под подзаголовок. Формула client_time не менялась. Блок 08 переименован в «Поиск заказов» и оформлен как третий сложный блок: строка базового минимума 2 часа в день × 5 дней с зелёной галочкой, раскрытие с семью зелёными задачами, синее уведомление о дополнительной нагрузке и нейтральная плашка с обоснованием. Формула promo_per_day не менялась. Зелёные галочки у строк со значениями по умолчанию уменьшены до размера синих информационных значков. Зелёные карточки раскрытий смягчены полупрозрачным градиентом. Строка о замере реальных проектов в блоке 07 перенесена под подзаголовок. Зелёные галочки у строк значений по умолчанию: круг 21 px с линейной зелёной обводкой, выравнивание по основному тексту — left 0, top 2 px; с синими уведомлениями не выравниваются. Зелёные галочки у значений по умолчанию переведены в линейный вариант: прозрачный круг, зелёная обводка и зелёная галочка. Зелёные маркеры значений по умолчанию: узкий указатель шириной 24 px и высотой в две строки, без галочки; углы и переход к треугольному окончанию слегка скруглены. Блок 12 обновлён: дома аренда/аналог жилья и коммунальные услуги умножаются на долю рабочей площади; при аренде помещения оба расхода учитываются полностью. Галочка own_home больше не отключает home_rent, а показывает рекомендацию указать рыночную аренду аналога или ипотечный платёж. Добавлено синее уведомление для режима офиса. Обводка указателей в блоках «Работа с клиентом» и «Поиск заказов» заменена на цвет неактивных полей c-ln (#E5E7EB). Декоративные зелёные маркеры у строк значений по умолчанию в блоках «Работа с клиентом» и «Поиск заказов» полностью удалены. Подсказка «Разработка, дизайн, наполнение…» под полем стоимости сайта удалена. Контекстные тексты блоков 07 и 08 вынесены из белых карточек и размещены сразу под ними как большие контурные уведомления на синем фоне раздела. При исключении FormClientTime время client_time обнуляется внутри расчёта; при исключении FormPromoTime обнуляется promo_per_day × net_days. Значения в полях сохраняются, карточки приглушаются по общему правилу EXC. Расстояние от верхнего объекта до заголовка — 34 px на десктопе и 28 px на мобильных; после подзаголовка до следующего блока — 38/30 px. Все уведомления, вынесенные из карточек прямо на цветной фон, приведены к стилю уведомления «Поиск заказов»: главный тезис 25–32 px (24 px на мобильных), пояснения 14,5 px с межстрочным интервалом 1,65 и едиными смысловыми отступами.</t>
         </is>
       </c>
     </row>
@@ -26129,7 +26136,7 @@
       </c>
       <c r="B419" s="229" t="inlineStr">
         <is>
-          <t>«Теперь посчитаем расходы» → «Учтём все расходы». Подзаголовок сокращён до двух строк: всё, на что уже потратились или тратитесь регулярно; чем точнее внесёте, тем ближе к правде ставка — можете воспользоваться значениями по умолчанию.</t>
+          <t>Раздел «Учтём все расходы». Над заголовком размещены три плашки по образцу «Приступим к расчёту»: «Ваши / инвестиции», «Периодические / платежи», «Отчисления / государству». Под заголовком остаётся: «Если расход не заложен в цену, вы оплачиваете из собственного кармана». Служебные повторы о готовых списках, редактировании и значениях по умолчанию удалены. Карточки 09–17 объединены общей градиентной подложкой; фоновая иллюстрация удалена. Цветовая гамма группы расходов заменена на Instagram-градиент блока 08 отчёта: фиолетовый → малиновый → коралловый. Дизайн баннера: одна компактная информационная плашка сверху, крупный заголовок Prata и вторичная строка снизу. Белые карточки расходов получили такой же лёгкий полупрозрачный градиент, как карточки времени. Текст «Не включайте сюда специфическое оборудование…» вынесен в единое синее информационное уведомление. Нижний цветной выступ группы расходов унифицирован до 42 px. Нижний цветной выступ всех групп приведён к референсу первых трёх блоков: 42 px на десктопе и 34 px на мобильном. После блока 10 добавлено крупное уведомление о расчёте по текущей рыночной стоимости оборудования или актуального аналога, а не по закупочной цене. Плашка оформлена как контурная вставка с тонкой полупрозрачной белой заливкой прямо на Instagram-фоне: белая типографика, белая полупрозрачная рамка и боковые отступы; внутренняя разметка сохранена. Уведомление о рыночной стоимости оборудования получило стандартный синий знак «!». Тексты блока 11 «Программное обеспечение», подписок и разовых лицензий обновлены. Финальная структура баннера: одна эмоциональная плашка, крупный заголовок и короткая вторичная мысль. Значок уведомления о рыночной стоимости — белый круг с красно-малиновым знаком; в правом нижнем углу добавлены полупрозрачные фоновые круги. Под блоком обучения добавлено постоянное уведомление об упущенной выгоде в стиле уведомления о рыночной стоимости оборудования. В блоке 12 два пояснения — о рабочем месте в найме и о самостоятельном обустройстве — вынесены в стандартные синие информационные уведомления. Расстояние от верхнего объекта до заголовка — 34 px на десктопе и 28 px на мобильных; после подзаголовка до следующего блока — 38/30 px. Все уведомления, вынесенные из карточек прямо на цветной фон, приведены к стилю уведомления «Поиск заказов»: главный тезис 25–32 px (24 px на мобильных), пояснения 14,5 px с межстрочным интервалом 1,65 и едиными смысловыми отступами. Иконка инвестиций заменена на портфель. Все подписи оформлены ровно в две строки.</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26148,7 @@
       </c>
       <c r="B420" s="229" t="inlineStr">
         <is>
-          <t>Карточек стало 20 вместо 16. Разделы .sect номеров не носят.</t>
+          <t>Карточек остаётся 20. «Готовых кадров за 1 час» перенесён из раздела времени в основные параметры сразу после «Ваша текущая ставка» и получил номер 04; «Минимальный выезд» стал блоком 05. Основные карточки 01–06, кроме налогового блока 02, используют статус «Основной параметр». Номера блоков сделаны заметнее: полупрозрачный тёмный цвет и mix-blend-mode:multiply меняют оттенок в зависимости от подложки. Подложка основных параметров сохраняет чёткие края и непрозрачную заливку: от середины блока 02 цвет постепенно меняется от почти чёрного к более светлому серо-коричневому (#6b6763) у нижнего края.</t>
         </is>
       </c>
     </row>
@@ -26157,6 +26164,18 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>ПЛАВАЮЩАЯ ПЛАШКА ДОВЕРИЯ</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>После прокрутки 500 px сверху появляется полупрозрачное меню в стиле .fbar отчёта. В нём размещены логотип, кириллическое слово «счётикс», значок пробного режима, кнопка «Поделиться», кнопка «Поблагодарить проект» и крестик. Нижняя подпись «твоя юнит-экономика» не используется. Все элементы выровнены по вертикальному центру. Пропорция надписи и знака повторяет основной логотип: 19/62 в шапке и 14/46 в плавающем меню; на мобильных 12,5/38. Цвет названия совпадает с цветом иконки «Поделиться».</t>
+        </is>
+      </c>
+    </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
@@ -26217,7 +26236,7 @@
       </c>
       <c r="B428" s="229" t="inlineStr">
         <is>
-          <t>«Подобрать режим автоматически», стоит по умолчанию. Под ней правило: из доступных режимов берём тот, где на руки остаётся больше; учитываем ставку, взносы и лимиты. Снял галочку — выбирай сам, список разблокируется.</t>
+          <t>«Подбирать режим автоматически» работает как переключатель. Первое нажатие включает постоянный подбор лучшего доступного режима с учётом ставки, взносов и лимитов; повторное нажатие отключает автоподбор и возвращает ручное управление налоговыми полями.</t>
         </is>
       </c>
     </row>
@@ -26253,7 +26272,7 @@
       </c>
       <c r="B431" s="229" t="inlineStr">
         <is>
-          <t>Убрано «из списка она убрана» и «между режимами ИП выбирать можно» — это описание нашей механики, а не ответ на вопрос «что мне делать». Написано: чтобы вернуться на самозанятость, нужно уменьшить желаемый доход в первом блоке; советуем сначала заполнить анкету до конца — когда будут учтены все расходы, станет ясно, насколько его надо менять.</t>
+          <t>Автоматический возврат работает только если пользователь первоначально сам выбрал НПД, а калькулятор временно заменил его из-за превышения лимита. При корректировке данных модель отдельно пересчитывается в НПД; если предполагаемая выручка снова не превышает 2 400 000 ₽, НПД восстанавливается. Если пользователь изначально выбрал ИП или вручную сменил автоматически выбранный режим, уведомления о НПД не показываются.</t>
         </is>
       </c>
     </row>
@@ -26265,7 +26284,7 @@
       </c>
       <c r="B432" s="229" t="inlineStr">
         <is>
-          <t>Расчёт по умолчанию не изменился: 60 полей, ноль расхождений. Строчка возврата появляется по изменению и возвращает цифру. Автоподбор при доходе 250 000 переставил НПД на УСН 6%.</t>
+          <t>Проверены сценарии: НПД → превышение → УСН 6% и жёлтое уведомление; возврат данных в лимит → НПД и зелёное уведомление; закрытое жёлтое уведомление не мешает показать зелёное; ручной выбор ИП не меняется и уведомлений НПД не вызывает. Проверено автоскрытие обоих состояний и сохранение исходного 12-секундного таймера при повторных пересчётах.</t>
         </is>
       </c>
     </row>
@@ -26309,7 +26328,7 @@
       </c>
       <c r="B437" s="229" t="inlineStr">
         <is>
-          <t>При включённом автоподборе блокируется не только список режимов, но и вопрос «С кем вы чаще работаете» — от него зависит ставка НПД, значит он тоже часть выбора. Обе галочки, автоподбор и «не учитывать блок», согласованы: каждая проверяет состояние другой.</t>
+          <t>При включённом автоподборе блокируется весь налоговый блок, включая саму кнопку автоподбора и «Не учитывать этот блок». Активной остаётся только локальная иконка сброса, которая возвращает ручной режим. Во включённом состоянии кнопка автоподбора остаётся насыщенной и яркой; затемняются остальные элементы блока, активен только локальный сброс.</t>
         </is>
       </c>
     </row>
@@ -26341,7 +26360,7 @@
       </c>
       <c r="B441" s="229" t="inlineStr">
         <is>
-          <t>«Всё введённое будет стёрто — нажмите ещё раз». Слово «стёрто» пугало и было неточным: поля не опустеют, а вернутся к исходным цифрам.</t>
+          <t>«Всё введённое будет стёрто — нажмите ещё раз». Слово «стёрто» пугало и было неточным: поля не опустеют, а вернутся к исходным цифрам. Все текстовые, числовые поля и списки получили состояния заполненности: если одно из полей строки равно нулю или пусто, вся строка становится светло-серой. Фон полей при этом прозрачный, без отдельной белой или серой заливки. Полностью заполненная строка получает мягкую зелёную рамку и подложку; фокус использует прежний активный стиль.</t>
         </is>
       </c>
     </row>
@@ -26521,7 +26540,7 @@
       </c>
       <c r="B460" s="229" t="inlineStr">
         <is>
-          <t>«Подобрать» → «Подбирать режим автоматически»: подбор идёт постоянно, при каждом изменении цифр, а не один раз по нажатию.</t>
+          <t>Кнопка «Подбирать режим автоматически» остаётся активной во включённом состоянии. Под ней показана подсказка «Нажмите повторно, чтобы отключить автоматический подбор». Локальный сброс по-прежнему возвращает весь налоговый блок к значениям по умолчанию.</t>
         </is>
       </c>
     </row>
@@ -26625,7 +26644,7 @@
       </c>
       <c r="B470" s="229" t="inlineStr">
         <is>
-          <t>«Работаю без оформления» в блоке налогов · «Живу в своём, ипотеки нет» в рабочем месте · «Не учитывать упущенную выгоду» в обучении · плашка о лимите налогового режима.</t>
+          <t>«Работаю без оформления» в блоке налогов · «Живу в своём, ипотеки нет» в рабочем месте · плашка о лимите налогового режима.</t>
         </is>
       </c>
     </row>
@@ -26637,7 +26656,7 @@
       </c>
       <c r="B471" s="229" t="inlineStr">
         <is>
-          <t>Под «Не учитывать упущенную выгоду» его не было вовсе. Написано: упущенная выгода — деньги, которые вы не заработали, пока учились; во время курса вы не снимали и не получали дохода; обычно её тоже закладывают в стоимость обучения, ведь потрачены и деньги, и рабочее время; если снять галочку, в расчёт войдёт только цена самих курсов.</t>
+          <t>Под блоком обучения добавлено постоянное контурное уведомление «Упущенная выгода — рекомендуем учитывать в расчёте». Пояснение охватывает время, вложенное в получение профессии, создание сайта и другие необходимые для работы задачи. Упущенная выгода учитывается автоматически, пока блок обучения включён; при отключении всего блока обучения в расчёт не входит.</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26688,7 @@
       </c>
       <c r="B474" s="229" t="inlineStr">
         <is>
-          <t>Одна строка на карточку, внизу перед «не учитывать этот блок». 20 карточек — 20 строк. Возвращает всё содержимое блока: поля, ползунки, переключатели, галочки и строки таблиц расходов.</t>
+          <t>Все локальные кнопки сброса перенесены к заголовкам карточек. В обычном блоке иконка стоит справа от h2. В составных блоках «Программное обеспечение» и «Банковское обслуживание» отдельные сбросы стоят напротив подзаголовков каждой самостоятельной формы. Кнопки больше не теряются рядом с «Добавить…» или полями. Под общей кнопкой «Вернуть значения по умолчанию» добавлены увеличенные иконки «Поделиться» и «Поблагодарить проект» с отступом 24 px и кнопками 46×46 px.</t>
         </is>
       </c>
     </row>
@@ -26705,7 +26724,19 @@
       </c>
       <c r="B477" s="229" t="inlineStr">
         <is>
-          <t>20 строк на 20 карточек, на старте ни одна не видна. Правка дохода — появилась в блоке 01. Галочка резерва — в блоке 18. Удаление строки таблицы — в блоке 09, после возврата строк снова 10. Расчёт не изменился: 60 полей, ноль расхождений.</t>
+          <t>Проверено: сбросы отсутствуют у полей и кнопок «Добавить…»; у программного обеспечения и банковского обслуживания по два сброса в строках подзаголовков; изменение и возврат таблиц работают. Расчётная логика не изменилась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ДЕКОРАТИВНЫЕ КРУГИ И НОМЕРА БЛОКОВ</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>В трёх карточках условий труда фоновые круги больше не повторяются: в первой два круга разных размеров, во второй один, в третьей два с другой композицией. Номера блоков получили более контрастный полупрозрачный цвет и режим смешивания с фоном.</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26808,6 @@
         </is>
       </c>
     </row>
-    <row r="485"/>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
@@ -27883,7 +27913,7 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Нанимаю бухгалтера — расход 120 000 ₽, время 0. Веду сам — расход 0, время 12 ч</t>
+          <t>Нанимаю специалиста — расход 120 000 ₽, время 0. Веду самостоятельно — расход 0, время 12 ч</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -27920,31 +27950,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Упущенная выгода</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>edu_mode</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>Учитывать — добавляет месяцы учёбы × доход. Только стоимость — 0</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Form006 · Block10</t>
-        </is>
-      </c>
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -30195,12 +30205,12 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>ед.: ₽/год · зависит от: ws_mode, own_home, home_rent, cab_share, home_util, office_rent, office_util</t>
+          <t>ед.: ₽/год · зависит от: ws_mode, home_rent, cab_share, home_util, office_rent, office_util</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>IF(ws_mode="Работаю из дома",(IF(own_home="да",0,home_rent)*cab_share+home_util)*months,(office_rent+office_util)*months)</t>
+          <t>IF(ws_mode="Работаю из дома",(home_rent+home_util)*cab_share*months,(office_rent+office_util)*months)</t>
         </is>
       </c>
     </row>
@@ -30297,27 +30307,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="14" t="inlineStr">
-        <is>
-          <t>ПЕРЕКЛЮЧАТЕЛЬ · упущенная выгода</t>
-        </is>
-      </c>
-      <c r="B138" s="15" t="inlineStr">
-        <is>
-          <t>edu_mode</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="D138" s="14" t="inlineStr"/>
-      <c r="E138" s="14" t="inlineStr">
-        <is>
-          <t>Учитывать упущенную выгоду</t>
-        </is>
-      </c>
+      <c r="A138" s="14" t="n"/>
+      <c r="B138" s="15" t="n"/>
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -30337,12 +30331,12 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>ед.: ₽ · зависит от: edu_mode, edu_months, income_month</t>
+          <t>ед.: ₽ · зависит от: edu_months, income_month</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>IF(edu_mode="Учитывать упущенную выгоду",edu_months*income_month,0)</t>
+          <t>edu_months*income_month</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30755,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Бухгалтер · стоимость в месяц</t>
+          <t>Специалист по учёту · стоимость в месяц</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
@@ -30788,7 +30782,7 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Переменные · бухгалтер</t>
+          <t>Переменные · специалист по учёту</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -30808,7 +30802,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>IF(acc_mode="Нанимаю бухгалтера",acc_cost_month*months,0)</t>
+          <t>IF(acc_mode="Нанимаю специалиста",acc_cost_month*months,0)</t>
         </is>
       </c>
     </row>
@@ -40463,7 +40457,7 @@
       <c r="G65" s="6" t="inlineStr"/>
       <c r="H65" s="30" t="inlineStr">
         <is>
-          <t>Form005 · при «да» аренда обнуляется</t>
+          <t>Контекстная галочка: показывает рекомендацию, но не обнуляет стоимость жилья</t>
         </is>
       </c>
     </row>
@@ -40495,7 +40489,7 @@
       <c r="G66" s="6" t="inlineStr"/>
       <c r="H66" s="30" t="inlineStr">
         <is>
-          <t>по доле метров. Обнуляется при own_home = да</t>
+          <t>По доле метров; поле остаётся активным при own_home = да</t>
         </is>
       </c>
     </row>
@@ -40527,7 +40521,7 @@
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="30" t="inlineStr">
         <is>
-          <t>ЦЕЛИКОМ</t>
+          <t>По доле метров рабочего места</t>
         </is>
       </c>
     </row>
@@ -40700,7 +40694,7 @@
         </is>
       </c>
       <c r="C73" s="36">
-        <f>IF(ws_mode="Работаю из дома",(IF(own_home="да",0,home_rent)*cab_share+home_util)*months,(office_rent+office_util)*months)</f>
+        <f>IF(ws_mode="Работаю из дома",(home_rent+home_util)*cab_share*months,(office_rent+office_util)*months)</f>
         <v/>
       </c>
       <c r="D73" s="28" t="inlineStr">
@@ -40710,7 +40704,7 @@
       </c>
       <c r="E73" s="30" t="inlineStr">
         <is>
-          <t>IF(ws_mode="Работаю из дома",(IF(own_home="да",0,home_rent)*cab_share+home_util)*months,(office_rent+office_util)*months)</t>
+          <t>IF(ws_mode="Работаю из дома",(home_rent+home_util)*cab_share*months,(office_rent+office_util)*months)</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -40720,7 +40714,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>ws_mode, own_home, home_rent, cab_share, home_util, office_rent, office_util</t>
+          <t>ws_mode, home_rent, cab_share, home_util, office_rent, office_util</t>
         </is>
       </c>
       <c r="H73" s="30" t="inlineStr"/>
@@ -40863,34 +40857,14 @@
       <c r="H78" s="30" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>edu_mode</t>
-        </is>
-      </c>
-      <c r="B79" s="28" t="inlineStr">
-        <is>
-          <t>ПЕРЕКЛЮЧАТЕЛЬ · упущенная выгода</t>
-        </is>
-      </c>
-      <c r="C79" s="34" t="inlineStr">
-        <is>
-          <t>Учитывать упущенную выгоду</t>
-        </is>
-      </c>
-      <c r="D79" s="28" t="inlineStr"/>
-      <c r="E79" s="30" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="30" t="inlineStr">
-        <is>
-          <t>Form006 · A58</t>
-        </is>
-      </c>
+      <c r="A79" s="27" t="n"/>
+      <c r="B79" s="28" t="n"/>
+      <c r="C79" s="34" t="n"/>
+      <c r="D79" s="28" t="n"/>
+      <c r="E79" s="30" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="6" t="n"/>
+      <c r="H79" s="30" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="27" t="inlineStr">
@@ -40904,7 +40878,7 @@
         </is>
       </c>
       <c r="C80" s="38">
-        <f>IF(edu_mode="Учитывать упущенную выгоду",edu_months*income_month,0)</f>
+        <f>edu_months*income_month</f>
         <v/>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -40914,7 +40888,7 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>IF(edu_mode="Учитывать упущенную выгоду",edu_months*income_month,0)</t>
+          <t>edu_months*income_month</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -40924,7 +40898,7 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>edu_mode, edu_months, income_month</t>
+          <t>edu_months, income_month</t>
         </is>
       </c>
       <c r="H80" s="30" t="inlineStr"/>
@@ -41543,7 +41517,7 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>Бухгалтер · стоимость в месяц</t>
+          <t>Специалист по учёту · стоимость в месяц</t>
         </is>
       </c>
       <c r="C98" s="37" t="n">
@@ -41575,11 +41549,11 @@
       </c>
       <c r="B99" s="28" t="inlineStr">
         <is>
-          <t>Переменные · бухгалтер</t>
+          <t>Переменные · специалист по учёту</t>
         </is>
       </c>
       <c r="C99" s="36">
-        <f>IF(acc_mode="Нанимаю бухгалтера",acc_cost_month*months,0)</f>
+        <f>IF(acc_mode="Нанимаю специалиста",acc_cost_month*months,0)</f>
         <v/>
       </c>
       <c r="D99" s="28" t="inlineStr">
@@ -41589,7 +41563,7 @@
       </c>
       <c r="E99" s="30" t="inlineStr">
         <is>
-          <t>IF(acc_mode="Нанимаю бухгалтера",acc_cost_month*months,0)</t>
+          <t>IF(acc_mode="Нанимаю специалиста",acc_cost_month*months,0)</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -42397,7 +42371,7 @@
       <c r="G123" s="6" t="inlineStr"/>
       <c r="H123" s="30" t="inlineStr">
         <is>
-          <t>Form008 · Block15</t>
+          <t>Базовая 2,7%; добавленные банковские проценты учитываются отдельно</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43057,7 @@
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Нанимаю бухгалтера,Веду самостоятельно"</formula1>
+      <formula1>"Нанимаю специалиста,Веду самостоятельно"</formula1>
     </dataValidation>
     <dataValidation sqref="C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Заложить резерв,Не закладывать"</formula1>
@@ -43191,11 +43165,11 @@
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>Canon EOS R6 Mark II</t>
+          <t>Canon EOS R6 Mark II Body</t>
         </is>
       </c>
       <c r="C5" s="45" t="n">
-        <v>239999</v>
+        <v>166999</v>
       </c>
       <c r="D5" s="46" t="n">
         <v>3</v>
@@ -43223,11 +43197,11 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>Canon RF 24–105mm F4 L</t>
+          <t>Canon RF 24–105mm f/4.0 L IS USM</t>
         </is>
       </c>
       <c r="C6" s="45" t="n">
-        <v>159999</v>
+        <v>130999</v>
       </c>
       <c r="D6" s="46" t="n">
         <v>5</v>
@@ -48283,7 +48257,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Желаемый доход</t>
+          <t>Ваш желаемый доход</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -48357,7 +48331,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Минимальная съёмка</t>
+          <t>Минимальный выезд (часов)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -48668,12 +48642,12 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>ПЕРЕКЛЮЧАТЕЛЬ упущенной выгоды</t>
+          <t>Стоимость, месяцы обучения и срок окупаемости</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>edu_mode, dep_education</t>
+          <t>edu_opportunity, dep_education</t>
         </is>
       </c>
     </row>
@@ -48816,7 +48790,7 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ПЕРЕКЛЮЧАТЕЛЬ сам/бухгалтер</t>
+          <t>ПЕРЕКЛЮЧАТЕЛЬ сам/специалист</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -49135,7 +49109,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ваш доход</t>
+          <t>Ваш желаемый доход</t>
         </is>
       </c>
       <c r="E5" s="102" t="inlineStr">
@@ -49172,12 +49146,12 @@
       </c>
       <c r="G6" s="61" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>108 999</t>
+          <t>110 216</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -49298,7 +49272,7 @@
       </c>
       <c r="G9" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -49345,7 +49319,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Как мы считаем</t>
+          <t>Как мы считаем:</t>
         </is>
       </c>
       <c r="E10" s="102" t="inlineStr">
@@ -49387,7 +49361,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Работа на себя должна делать вашу жизнь лучше, а не превращать её в бесконечную работу. Поэтому в расчётах Счётикс мы ориентируемся на нормы трудового законодательства РФ и производственный календарь — чтобы у вас оставались силы на творчество, развитие и жизнь вне работы.</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr"/>
@@ -49435,7 +49409,11 @@
       </c>
       <c r="F12" s="103" t="n"/>
       <c r="G12" s="103" t="n"/>
-      <c r="H12" s="103" t="n"/>
+      <c r="H12" s="103" t="inlineStr">
+        <is>
+          <t>Время — ваш главный рабочий ресурс. Три плашки: «Всё рабочее время», «Невидимая нагрузка», «Честная стоимость часа». Каждая содержит крупную иконку и короткий тезис. Под заголовком: «Посчитаем время, которое обычно остаётся невидимым».</t>
+        </is>
+      </c>
       <c r="I12" s="103" t="n"/>
       <c r="J12" s="103" t="n"/>
       <c r="K12" s="103" t="n"/>
@@ -49447,7 +49425,7 @@
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Часов обработки на 1 час съёмки</t>
+          <t>Время на постпродакшн</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -49462,7 +49440,7 @@
       </c>
       <c r="G13" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -49493,12 +49471,12 @@
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Часов на клиента (1 проект)</t>
+          <t>Работа с клиентом (на один проект)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>поле ввода</t>
+          <t>поле ввода · блок можно исключить</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -49508,7 +49486,7 @@
       </c>
       <c r="G14" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -49539,12 +49517,12 @@
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Продвижение</t>
+          <t>Поиск заказов</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>поле ввода</t>
+          <t>поле ввода · блок можно исключить</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -49554,7 +49532,7 @@
       </c>
       <c r="G15" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -49585,7 +49563,7 @@
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Длительность съёмки</t>
+          <t>Минимальный выезд (часов)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -49600,7 +49578,7 @@
       </c>
       <c r="G16" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -49633,7 +49611,7 @@
       <c r="C17" s="17" t="inlineStr"/>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Моя обычная съёмка</t>
+          <t>Готовых кадров за 1 час</t>
         </is>
       </c>
       <c r="E17" s="17" t="inlineStr">
@@ -49648,7 +49626,7 @@
       </c>
       <c r="G17" s="105" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>52% + кнопка сброса</t>
         </is>
       </c>
       <c r="H17" s="17" t="n">
@@ -49979,7 +49957,7 @@
       <c r="C25" s="20" t="inlineStr"/>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Canon EOS R6 Mark II</t>
+          <t>Canon EOS R6 Mark II Body</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -49999,7 +49977,7 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>239 999 ₽ / 3 лет</t>
+          <t>166 999 ₽ / 3 лет</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr"/>
@@ -50017,7 +49995,7 @@
       <c r="C26" s="20" t="inlineStr"/>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Canon RF 24–105mm F4 L</t>
+          <t>Canon RF 24–105mm f/4.0 L IS USM</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -50037,7 +50015,7 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>159 999 ₽ / 5 лет</t>
+          <t>130 999 ₽ / 5 лет</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr"/>
@@ -51021,7 +50999,11 @@
       </c>
       <c r="F51" s="103" t="n"/>
       <c r="G51" s="103" t="n"/>
-      <c r="H51" s="103" t="n"/>
+      <c r="H51" s="103" t="inlineStr">
+        <is>
+          <t>Укажите программы и сервисы, которые нужны вам для профессиональной деятельности и работы вокруг неё.</t>
+        </is>
+      </c>
       <c r="I51" s="103" t="n"/>
       <c r="J51" s="103" t="n"/>
       <c r="K51" s="103" t="n"/>
@@ -51093,7 +51075,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Лицензии и сервисы, за которые вы регулярно платите.</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
@@ -51337,7 +51323,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Программы и лицензии, которые вы оплачивали один раз и используете длительное время.</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr">
         <is>
@@ -51694,7 +51684,7 @@
       </c>
       <c r="E68" s="102" t="inlineStr">
         <is>
-          <t>переключатель меняет набор полей</t>
+          <t>переключатель; дома аренда и коммунальные считаются по доле площади, офис — полностью</t>
         </is>
       </c>
       <c r="F68" s="103" t="n"/>
@@ -51819,7 +51809,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>40 000</t>
+          <t>40 000; строка обязательная, без удаления</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -51869,7 +51859,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>7 000; строку можно удалить</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -51919,7 +51909,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>50; строку можно удалить</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -51969,7 +51959,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6; строку можно удалить</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -52635,42 +52625,14 @@
       <c r="A90" s="5" t="inlineStr"/>
       <c r="B90" s="5" t="inlineStr"/>
       <c r="C90" s="5" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Учитывать упущенный доход</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>галочка</t>
-        </is>
-      </c>
-      <c r="F90" s="15" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="G90" s="61" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>включена</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Form006</t>
-        </is>
-      </c>
-      <c r="K90" s="6" t="inlineStr">
-        <is>
-          <t>edu_mode</t>
-        </is>
-      </c>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="15" t="n"/>
+      <c r="G90" s="61" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="6" t="n"/>
       <c r="L90" s="5" t="inlineStr">
         <is>
           <t>если включена: + месяцев × желаемый доход</t>
@@ -52788,7 +52750,7 @@
       </c>
       <c r="E93" s="102" t="inlineStr">
         <is>
-          <t>переключатель меняет поля</t>
+          <t>переключатель; поля зафиксированы в двухколоночной сетке</t>
         </is>
       </c>
       <c r="F93" s="103" t="n"/>
@@ -53574,7 +53536,7 @@
       </c>
       <c r="E112" s="102" t="inlineStr">
         <is>
-          <t>две части: платежи и процент</t>
+          <t>две независимые части: регулярные платежи и комиссии банка</t>
         </is>
       </c>
       <c r="F112" s="103" t="n"/>
@@ -53877,12 +53839,12 @@
       <c r="C120" s="5" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>— Комиссия с оборота</t>
+          <t>— Комиссии банка</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>подзаголовок</t>
+          <t>таблица «Позиция / Ставка» с добавляемыми комиссиями</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
@@ -53915,27 +53877,27 @@
       <c r="C121" s="5" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Ставка эквайринга</t>
+          <t>Эквайринг</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>поле ввода</t>
+          <t>строка таблицы: поле позиции + ставка</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>input_number</t>
+          <t>table_row</t>
         </is>
       </c>
       <c r="G121" s="61" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>Эквайринг / 2,7; строку можно удалить</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -53961,7 +53923,7 @@
       <c r="C122" s="5" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Доля безналичных оплат</t>
+          <t>Доля оплат через эквайринг</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -53981,7 +53943,7 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>100; удаляется вместе со строкой эквайринга</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -54001,7 +53963,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>если часть клиентов платит переводом — уменьшите</t>
+          <t>отдельная строка под таблицей; вопрос оформлен как поле и удаляется вместе со строкой эквайринга</t>
         </is>
       </c>
     </row>
@@ -54123,7 +54085,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2 варианта: Веду самостоятельно / Нанимаю бухгалтера</t>
+          <t>2 варианта: Веду самостоятельно / Нанимаю специалиста</t>
         </is>
       </c>
     </row>
@@ -54183,7 +54145,7 @@
       <c r="C127" s="5" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Стоимость бухгалтера</t>
+          <t>Стоимость специалиста</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -54223,7 +54185,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>видно при «Нанимаю». Уходит в ДЕНЬГИ, время = 0</t>
+          <t>видно при «Нанимаю специалиста». Уходит в ДЕНЬГИ, время = 0</t>
         </is>
       </c>
     </row>
